--- a/E2/protocol/visca/VISCA Command.xlsx
+++ b/E2/protocol/visca/VISCA Command.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Command" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="873">
   <si>
     <t>Command Set</t>
   </si>
@@ -394,6 +394,12 @@
     <t>8x 01 7E 04 56 02 0p 0q 0r 0s FF</t>
   </si>
   <si>
+    <t>R Offset(Color Temerature Mode)</t>
+  </si>
+  <si>
+    <t>B Offset(Color Temerature Mode)</t>
+  </si>
+  <si>
     <t>Color Temperature</t>
   </si>
   <si>
@@ -445,13 +451,13 @@
     <t>8x 01 04 39 00 FF</t>
   </si>
   <si>
-    <t>固定Iris，Shutter/Gain Auto</t>
+    <t>Iris Manual，Shutter/Gain Auto</t>
   </si>
   <si>
     <t>8x 01 04 39 03 FF</t>
   </si>
   <si>
-    <t>Iris/Shutter/Gain手动</t>
+    <t>Iris/Shutter/Gain Manual</t>
   </si>
   <si>
     <t>Shutter Priority</t>
@@ -460,7 +466,7 @@
     <t>8x 01 04 39 0A FF</t>
   </si>
   <si>
-    <t>Iris/Shutter手动, Gain Auto</t>
+    <t>Iris/Shutter Manaul, Gain Auto</t>
   </si>
   <si>
     <t>Iris Priority</t>
@@ -844,6 +850,60 @@
   </si>
   <si>
     <t>pp: 00 - 0xC8,   64 is default</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>8x 01 7E 03 15 0p FF</t>
+  </si>
+  <si>
+    <t>Master</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>8x 01 7E 05 15 00 FF</t>
+  </si>
+  <si>
+    <t>8x 01 7E 05 15 02 FF</t>
+  </si>
+  <si>
+    <t>8x 01 7E 05 15 03 FF</t>
+  </si>
+  <si>
+    <t>8x 01 7E 05 45 0p 0p FF</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>8x 01 7E 06 15 00 FF</t>
+  </si>
+  <si>
+    <t>8x 01 7E 06 15 02 FF</t>
+  </si>
+  <si>
+    <t>8x 01 7E 06 15 03 FF</t>
+  </si>
+  <si>
+    <t>8x 01 7E 06 45 0p 0p FF</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>8x 01 7E 07 15 00 FF</t>
+  </si>
+  <si>
+    <t>8x 01 7E 07 15 02 FF</t>
+  </si>
+  <si>
+    <t>8x 01 7E 07 15 03 FF</t>
+  </si>
+  <si>
+    <t>8x 01 7E 07 45 0p 0p FF</t>
   </si>
   <si>
     <t>Pan Tilt</t>
@@ -2407,6 +2467,9 @@
   </si>
   <si>
     <t>1/8000</t>
+  </si>
+  <si>
+    <t>1/10000</t>
   </si>
   <si>
     <t>Zoom (24x)</t>
@@ -2817,6 +2880,12 @@
       <sz val="11"/>
       <color rgb="FF182B50"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF182B50"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2962,12 +3031,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF182B50"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="37">
@@ -3449,16 +3512,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3467,119 +3527,122 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3651,6 +3714,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3966,18 +4047,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E168"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="16.5" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="22" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6272727272727" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.2545454545455" style="1" customWidth="1"/>
     <col min="4" max="4" width="41.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="46.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="46.2545454545455" style="1" customWidth="1"/>
     <col min="6" max="16384" width="10" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="1" s="1" customFormat="1" ht="19.5" customHeight="1" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3992,7 +4073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="2" s="1" customFormat="1" ht="18" customHeight="1" spans="1:5">
       <c r="A2" s="2"/>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -4031,7 +4112,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="1:5">
       <c r="A5" s="20"/>
       <c r="B5" s="4" t="s">
         <v>12</v>
@@ -4044,7 +4125,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="1:5">
       <c r="A6" s="20"/>
       <c r="B6" s="4" t="s">
         <v>15</v>
@@ -4092,7 +4173,7 @@
       </c>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="1:5">
       <c r="A10" s="20"/>
       <c r="B10" s="4" t="s">
         <v>24</v>
@@ -4136,7 +4217,7 @@
       </c>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="1:5">
       <c r="A14" s="2"/>
       <c r="B14" s="23"/>
       <c r="C14" s="23"/>
@@ -4449,7 +4530,7 @@
       <c r="A37" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="24" t="s">
         <v>48</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -4464,7 +4545,7 @@
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A38" s="14"/>
-      <c r="B38" s="14"/>
+      <c r="B38" s="25"/>
       <c r="C38" s="4" t="s">
         <v>89</v>
       </c>
@@ -4477,7 +4558,7 @@
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A39" s="14"/>
-      <c r="B39" s="14"/>
+      <c r="B39" s="25"/>
       <c r="C39" s="4" t="s">
         <v>92</v>
       </c>
@@ -4490,7 +4571,7 @@
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A40" s="14"/>
-      <c r="B40" s="14"/>
+      <c r="B40" s="25"/>
       <c r="C40" s="4" t="s">
         <v>95</v>
       </c>
@@ -4501,7 +4582,7 @@
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A41" s="14"/>
-      <c r="B41" s="14"/>
+      <c r="B41" s="25"/>
       <c r="C41" s="4" t="s">
         <v>97</v>
       </c>
@@ -4514,7 +4595,7 @@
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A42" s="14"/>
-      <c r="B42" s="14"/>
+      <c r="B42" s="26"/>
       <c r="C42" s="4" t="s">
         <v>100</v>
       </c>
@@ -4542,7 +4623,7 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A44" s="14"/>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="9" t="s">
         <v>106</v>
       </c>
       <c r="C44" s="4" t="s">
@@ -4555,7 +4636,7 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A45" s="14"/>
-      <c r="B45" s="14"/>
+      <c r="B45" s="9"/>
       <c r="C45" s="4" t="s">
         <v>109</v>
       </c>
@@ -4566,7 +4647,7 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A46" s="14"/>
-      <c r="B46" s="14"/>
+      <c r="B46" s="9"/>
       <c r="C46" s="4" t="s">
         <v>111</v>
       </c>
@@ -4577,7 +4658,7 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A47" s="14"/>
-      <c r="B47" s="14"/>
+      <c r="B47" s="9"/>
       <c r="C47" s="4" t="s">
         <v>59</v>
       </c>
@@ -4590,7 +4671,7 @@
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A48" s="14"/>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="9" t="s">
         <v>115</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -4603,7 +4684,7 @@
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A49" s="14"/>
-      <c r="B49" s="14"/>
+      <c r="B49" s="9"/>
       <c r="C49" s="4" t="s">
         <v>109</v>
       </c>
@@ -4614,7 +4695,7 @@
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A50" s="14"/>
-      <c r="B50" s="14"/>
+      <c r="B50" s="9"/>
       <c r="C50" s="4" t="s">
         <v>111</v>
       </c>
@@ -4625,7 +4706,7 @@
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A51" s="14"/>
-      <c r="B51" s="14"/>
+      <c r="B51" s="9"/>
       <c r="C51" s="4" t="s">
         <v>59</v>
       </c>
@@ -4638,314 +4719,314 @@
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A52" s="14"/>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="9" t="s">
         <v>107</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>122</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="E52" s="9"/>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A53" s="14"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="4" t="s">
+      <c r="B53" s="9"/>
+      <c r="C53" s="9" t="s">
         <v>109</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E53" s="4"/>
+        <v>110</v>
+      </c>
+      <c r="E53" s="9"/>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A54" s="14"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="4" t="s">
+      <c r="B54" s="9"/>
+      <c r="C54" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E54" s="4"/>
+        <v>112</v>
+      </c>
+      <c r="E54" s="9"/>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A55" s="14"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="4" t="s">
+      <c r="B55" s="9"/>
+      <c r="C55" s="9" t="s">
         <v>59</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>126</v>
+        <v>113</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A56" s="14"/>
-      <c r="B56" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C56" s="4" t="s">
+      <c r="B56" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C56" s="9" t="s">
         <v>107</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>129</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="E56" s="9"/>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A57" s="14"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="4" t="s">
+      <c r="B57" s="9"/>
+      <c r="C57" s="9" t="s">
         <v>109</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E57" s="4"/>
+        <v>117</v>
+      </c>
+      <c r="E57" s="9"/>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A58" s="14"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="4" t="s">
+      <c r="B58" s="9"/>
+      <c r="C58" s="9" t="s">
         <v>111</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E58" s="4"/>
+        <v>118</v>
+      </c>
+      <c r="E58" s="9"/>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A59" s="14"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="4" t="s">
+      <c r="B59" s="9"/>
+      <c r="C59" s="9" t="s">
         <v>59</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>133</v>
+        <v>119</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A60" s="2"/>
-      <c r="B60" s="23"/>
-      <c r="C60" s="23"/>
-      <c r="D60" s="23"/>
-      <c r="E60" s="23"/>
+      <c r="A60" s="14"/>
+      <c r="B60" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A61" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>48</v>
-      </c>
+      <c r="A61" s="14"/>
+      <c r="B61" s="9"/>
       <c r="C61" s="4" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>137</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="E61" s="4"/>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A62" s="14"/>
-      <c r="B62" s="14"/>
+      <c r="B62" s="9"/>
       <c r="C62" s="4" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>139</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="E62" s="4"/>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A63" s="14"/>
-      <c r="B63" s="14"/>
+      <c r="B63" s="9"/>
       <c r="C63" s="4" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A64" s="14"/>
-      <c r="B64" s="14"/>
+      <c r="B64" s="9" t="s">
+        <v>129</v>
+      </c>
       <c r="C64" s="4" t="s">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="65" s="1" customFormat="1" ht="54.75" customHeight="1" spans="1:5">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A65" s="14"/>
-      <c r="B65" s="4" t="s">
-        <v>145</v>
-      </c>
+      <c r="B65" s="9"/>
       <c r="C65" s="4" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="E65" s="21" t="s">
-        <v>147</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="E65" s="4"/>
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A66" s="14"/>
-      <c r="B66" s="4" t="s">
-        <v>148</v>
-      </c>
+      <c r="B66" s="9"/>
       <c r="C66" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>150</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="E66" s="4"/>
     </row>
     <row r="67" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A67" s="14"/>
-      <c r="B67" s="14"/>
+      <c r="B67" s="9"/>
       <c r="C67" s="4" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A68" s="14"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E68" s="4"/>
+      <c r="A68" s="2"/>
+      <c r="B68" s="23"/>
+      <c r="C68" s="23"/>
+      <c r="D68" s="23"/>
+      <c r="E68" s="23"/>
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A69" s="14"/>
-      <c r="B69" s="14"/>
+      <c r="A69" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="C69" s="4" t="s">
-        <v>59</v>
+        <v>137</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="E69" s="4"/>
+        <v>138</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="70" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A70" s="14"/>
-      <c r="B70" s="4" t="s">
-        <v>155</v>
-      </c>
+      <c r="B70" s="14"/>
       <c r="C70" s="4" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A71" s="14"/>
       <c r="B71" s="14"/>
       <c r="C71" s="4" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="E71" s="4"/>
+        <v>143</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A72" s="14"/>
       <c r="B72" s="14"/>
       <c r="C72" s="4" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E72" s="4"/>
-    </row>
-    <row r="73" s="1" customFormat="1" customHeight="1" spans="1:5">
+        <v>146</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="1" ht="54.75" customHeight="1" spans="1:5">
       <c r="A73" s="14"/>
-      <c r="B73" s="14"/>
+      <c r="B73" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="C73" s="4" t="s">
         <v>59</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E73" s="4"/>
+        <v>148</v>
+      </c>
+      <c r="E73" s="21" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A74" s="14"/>
-      <c r="B74" s="14"/>
+      <c r="B74" s="4" t="s">
+        <v>150</v>
+      </c>
       <c r="C74" s="4" t="s">
-        <v>161</v>
+        <v>107</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="E74" s="4"/>
+        <v>151</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A75" s="14"/>
-      <c r="B75" s="4" t="s">
-        <v>163</v>
-      </c>
+      <c r="B75" s="14"/>
       <c r="C75" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A76" s="14"/>
       <c r="B76" s="14"/>
       <c r="C76" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E76" s="4"/>
     </row>
@@ -4953,58 +5034,58 @@
       <c r="A77" s="14"/>
       <c r="B77" s="14"/>
       <c r="C77" s="4" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="E77" s="4"/>
     </row>
     <row r="78" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A78" s="14"/>
-      <c r="B78" s="14"/>
+      <c r="B78" s="4" t="s">
+        <v>157</v>
+      </c>
       <c r="C78" s="4" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E78" s="4"/>
+        <v>158</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="79" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A79" s="14"/>
       <c r="B79" s="14"/>
       <c r="C79" s="4" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>171</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="E79" s="4"/>
     </row>
     <row r="80" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A80" s="14"/>
       <c r="B80" s="14"/>
       <c r="C80" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>173</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="E80" s="4"/>
     </row>
     <row r="81" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A81" s="14"/>
       <c r="B81" s="14"/>
       <c r="C81" s="4" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="E81" s="4"/>
     </row>
@@ -5012,1229 +5093,1541 @@
       <c r="A82" s="14"/>
       <c r="B82" s="14"/>
       <c r="C82" s="4" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="E82" s="4"/>
     </row>
     <row r="83" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A83" s="14"/>
-      <c r="B83" s="14"/>
+      <c r="B83" s="4" t="s">
+        <v>165</v>
+      </c>
       <c r="C83" s="4" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E83" s="4"/>
+        <v>166</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="84" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A84" s="14"/>
-      <c r="B84" s="4" t="s">
-        <v>177</v>
-      </c>
+      <c r="B84" s="14"/>
       <c r="C84" s="4" t="s">
-        <v>178</v>
+        <v>109</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="E84" s="4" t="s">
-        <v>180</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="E84" s="4"/>
     </row>
     <row r="85" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A85" s="14"/>
-      <c r="B85" s="4" t="s">
-        <v>181</v>
-      </c>
+      <c r="B85" s="14"/>
       <c r="C85" s="4" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>183</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="E85" s="4"/>
     </row>
     <row r="86" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A86" s="2"/>
-      <c r="B86" s="23"/>
-      <c r="C86" s="23"/>
-      <c r="D86" s="23"/>
-      <c r="E86" s="23"/>
-    </row>
-    <row r="87" s="1" customFormat="1" ht="108.75" customHeight="1" spans="1:5">
-      <c r="A87" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>185</v>
-      </c>
+      <c r="A86" s="14"/>
+      <c r="B86" s="14"/>
+      <c r="C86" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E86" s="4"/>
+    </row>
+    <row r="87" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A87" s="14"/>
+      <c r="B87" s="14"/>
       <c r="C87" s="4" t="s">
-        <v>59</v>
+        <v>171</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="E87" s="21" t="s">
-        <v>187</v>
+        <v>172</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="88" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A88" s="20"/>
-      <c r="B88" s="4" t="s">
-        <v>188</v>
-      </c>
+      <c r="A88" s="14"/>
+      <c r="B88" s="14"/>
       <c r="C88" s="4" t="s">
         <v>107</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="E88" s="4"/>
+        <v>174</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="89" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A89" s="20"/>
+      <c r="A89" s="14"/>
       <c r="B89" s="14"/>
       <c r="C89" s="4" t="s">
         <v>109</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="E89" s="4"/>
     </row>
     <row r="90" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A90" s="20"/>
+      <c r="A90" s="14"/>
       <c r="B90" s="14"/>
       <c r="C90" s="4" t="s">
         <v>111</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="E90" s="4"/>
     </row>
     <row r="91" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A91" s="20"/>
+      <c r="A91" s="14"/>
       <c r="B91" s="14"/>
       <c r="C91" s="4" t="s">
         <v>59</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>193</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="E91" s="4"/>
     </row>
     <row r="92" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A92" s="20"/>
+      <c r="A92" s="14"/>
       <c r="B92" s="4" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="C92" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="93" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A93" s="14"/>
+      <c r="B93" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C93" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D92" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="93" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A93" s="20"/>
-      <c r="B93" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>59</v>
-      </c>
       <c r="D93" s="4" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A94" s="20"/>
-      <c r="B94" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="95" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A95" s="20"/>
+      <c r="A94" s="2"/>
+      <c r="B94" s="23"/>
+      <c r="C94" s="23"/>
+      <c r="D94" s="23"/>
+      <c r="E94" s="23"/>
+    </row>
+    <row r="95" s="1" customFormat="1" ht="108.75" customHeight="1" spans="1:5">
+      <c r="A95" s="18" t="s">
+        <v>186</v>
+      </c>
       <c r="B95" s="4" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>59</v>
       </c>
       <c r="D95" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E95" s="21" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="96" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A96" s="20"/>
+      <c r="B96" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E96" s="4"/>
+    </row>
+    <row r="97" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A97" s="20"/>
+      <c r="B97" s="14"/>
+      <c r="C97" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E97" s="4"/>
+    </row>
+    <row r="98" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A98" s="20"/>
+      <c r="B98" s="14"/>
+      <c r="C98" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E98" s="4"/>
+    </row>
+    <row r="99" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A99" s="20"/>
+      <c r="B99" s="14"/>
+      <c r="C99" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="100" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A100" s="20"/>
+      <c r="B100" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="101" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A101" s="20"/>
+      <c r="B101" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="102" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A102" s="20"/>
+      <c r="B102" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E102" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="E95" s="4" t="s">
+    </row>
+    <row r="103" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A103" s="20"/>
+      <c r="B103" s="4" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="96" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A96" s="19"/>
-      <c r="B96" s="4" t="s">
+      <c r="C103" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D103" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="E103" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="104" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A104" s="19"/>
+      <c r="B104" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C104" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D96" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="E96" s="4" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="97" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A97" s="4" t="s">
+      <c r="D104" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="E104" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C97" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="D97" s="4" t="s">
+    </row>
+    <row r="105" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A105" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="E97" s="4" t="s">
+      <c r="B105" s="4" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="98" s="1" customFormat="1" ht="257.25" customHeight="1" spans="1:5">
-      <c r="A98" s="14"/>
-      <c r="B98" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D98" s="4" t="s">
+      <c r="C105" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D105" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E98" s="21" t="s">
+      <c r="E105" s="4" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="99" s="1" customFormat="1" ht="68.25" customHeight="1" spans="1:5">
-      <c r="A99" s="14"/>
-      <c r="B99" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="E99" s="21" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="100" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A100" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="101" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A101" s="14"/>
-      <c r="B101" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="E101" s="22" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="102" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A102" s="14"/>
-      <c r="B102" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D102" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="E102" s="20"/>
-    </row>
-    <row r="103" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A103" s="14"/>
-      <c r="B103" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D103" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="E103" s="20"/>
-    </row>
-    <row r="104" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A104" s="14"/>
-      <c r="B104" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D104" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="E104" s="20"/>
-    </row>
-    <row r="105" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A105" s="14"/>
-      <c r="B105" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="E105" s="20"/>
-    </row>
-    <row r="106" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="106" s="1" customFormat="1" ht="257.25" customHeight="1" spans="1:5">
       <c r="A106" s="14"/>
       <c r="B106" s="4" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>34</v>
       </c>
       <c r="D106" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E106" s="21" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="107" s="1" customFormat="1" ht="68.25" customHeight="1" spans="1:5">
+      <c r="A107" s="14"/>
+      <c r="B107" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E107" s="21" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="108" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A108" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="109" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A109" s="14"/>
+      <c r="B109" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="E109" s="22" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="110" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A110" s="14"/>
+      <c r="B110" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E110" s="20"/>
+    </row>
+    <row r="111" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A111" s="14"/>
+      <c r="B111" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="E111" s="20"/>
+    </row>
+    <row r="112" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A112" s="14"/>
+      <c r="B112" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E112" s="20"/>
+    </row>
+    <row r="113" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A113" s="14"/>
+      <c r="B113" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D113" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="E106" s="19"/>
-    </row>
-    <row r="107" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A107" s="18" t="s">
+      <c r="E113" s="20"/>
+    </row>
+    <row r="114" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A114" s="14"/>
+      <c r="B114" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="C114" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D114" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="C107" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="D107" s="4" t="s">
+      <c r="E114" s="19"/>
+    </row>
+    <row r="115" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A115" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="E107" s="4" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="108" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A108" s="20"/>
-      <c r="B108" s="14"/>
-      <c r="C108" s="4" t="s">
+      <c r="B115" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="D108" s="4" t="s">
+      <c r="C115" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D115" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="E108" s="4" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="109" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A109" s="20"/>
-      <c r="B109" s="14"/>
-      <c r="C109" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="D109" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="E109" s="4" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="110" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A110" s="20"/>
-      <c r="B110" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="D110" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="E110" s="4" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="111" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A111" s="20"/>
-      <c r="B111" s="20"/>
-      <c r="C111" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="D111" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="E111" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="112" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A112" s="20"/>
-      <c r="B112" s="18" t="s">
-        <v>248</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="E112" s="4" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="113" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A113" s="20"/>
-      <c r="B113" s="19"/>
-      <c r="C113" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="E113" s="4" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="114" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A114" s="20"/>
-      <c r="B114" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="E114" s="4"/>
-    </row>
-    <row r="115" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A115" s="20"/>
-      <c r="B115" s="20"/>
-      <c r="C115" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D115" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="E115" s="4"/>
+      <c r="E115" s="4" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="116" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A116" s="20"/>
-      <c r="B116" s="20"/>
+      <c r="B116" s="14"/>
       <c r="C116" s="4" t="s">
-        <v>111</v>
+        <v>238</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="E116" s="4"/>
+        <v>239</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="117" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A117" s="20"/>
-      <c r="B117" s="19"/>
+      <c r="B117" s="14"/>
       <c r="C117" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="118" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A118" s="20"/>
+      <c r="B118" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="119" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A119" s="20"/>
+      <c r="B119" s="20"/>
+      <c r="C119" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="120" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A120" s="20"/>
+      <c r="B120" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="121" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A121" s="20"/>
+      <c r="B121" s="19"/>
+      <c r="C121" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="122" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A122" s="20"/>
+      <c r="B122" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E122" s="4"/>
+    </row>
+    <row r="123" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A123" s="20"/>
+      <c r="B123" s="20"/>
+      <c r="C123" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E123" s="4"/>
+    </row>
+    <row r="124" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A124" s="20"/>
+      <c r="B124" s="20"/>
+      <c r="C124" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E124" s="4"/>
+    </row>
+    <row r="125" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A125" s="20"/>
+      <c r="B125" s="19"/>
+      <c r="C125" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D117" s="4" t="s">
+      <c r="D125" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="126" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A126" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="B126" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="C126" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="D126" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="127" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A127" s="29"/>
+      <c r="B127" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="C127" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D127" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="E127" s="9"/>
+    </row>
+    <row r="128" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A128" s="29"/>
+      <c r="B128" s="24"/>
+      <c r="C128" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D128" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="E117" s="4" t="s">
+      <c r="E128" s="9"/>
+    </row>
+    <row r="129" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A129" s="29"/>
+      <c r="B129" s="24"/>
+      <c r="C129" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D129" s="28" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="118" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A118" s="24"/>
-      <c r="B118" s="11"/>
-      <c r="C118" s="11"/>
-      <c r="D118" s="11"/>
-      <c r="E118" s="11"/>
-    </row>
-    <row r="119" s="1" customFormat="1" ht="27.75" customHeight="1" spans="1:5">
-      <c r="A119" s="4" t="s">
+      <c r="E129" s="9"/>
+    </row>
+    <row r="130" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A130" s="29"/>
+      <c r="B130" s="24"/>
+      <c r="C130" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D130" s="28" t="s">
         <v>261</v>
       </c>
-      <c r="B119" s="4" t="s">
+      <c r="E130" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="C119" s="4" t="s">
+    </row>
+    <row r="131" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A131" s="29"/>
+      <c r="B131" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="C131" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D131" s="28" t="s">
+        <v>267</v>
+      </c>
+      <c r="E131" s="9"/>
+    </row>
+    <row r="132" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A132" s="29"/>
+      <c r="B132" s="24"/>
+      <c r="C132" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="D119" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="E119" s="21" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="120" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A120" s="14"/>
-      <c r="B120" s="14"/>
-      <c r="C120" s="4" t="s">
+      <c r="D132" s="28" t="s">
+        <v>268</v>
+      </c>
+      <c r="E132" s="9"/>
+    </row>
+    <row r="133" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A133" s="29"/>
+      <c r="B133" s="24"/>
+      <c r="C133" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="D120" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="E120" s="4"/>
-    </row>
-    <row r="121" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A121" s="14"/>
-      <c r="B121" s="14"/>
-      <c r="C121" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="E121" s="4"/>
-    </row>
-    <row r="122" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A122" s="14"/>
-      <c r="B122" s="14"/>
-      <c r="C122" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="D122" s="4" t="s">
+      <c r="D133" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="E122" s="4"/>
-    </row>
-    <row r="123" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A123" s="14"/>
-      <c r="B123" s="14"/>
-      <c r="C123" s="4" t="s">
+      <c r="E133" s="9"/>
+    </row>
+    <row r="134" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A134" s="29"/>
+      <c r="B134" s="24"/>
+      <c r="C134" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D134" s="28" t="s">
         <v>270</v>
       </c>
-      <c r="D123" s="4" t="s">
+      <c r="E134" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="135" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A135" s="29"/>
+      <c r="B135" s="24" t="s">
         <v>271</v>
       </c>
-      <c r="E123" s="4"/>
-    </row>
-    <row r="124" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A124" s="14"/>
-      <c r="B124" s="14"/>
-      <c r="C124" s="4" t="s">
+      <c r="C135" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D135" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="D124" s="4" t="s">
+      <c r="E135" s="9"/>
+    </row>
+    <row r="136" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A136" s="29"/>
+      <c r="B136" s="24"/>
+      <c r="C136" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D136" s="28" t="s">
         <v>273</v>
       </c>
-      <c r="E124" s="4"/>
-    </row>
-    <row r="125" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A125" s="14"/>
-      <c r="B125" s="14"/>
-      <c r="C125" s="4" t="s">
+      <c r="E136" s="9"/>
+    </row>
+    <row r="137" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A137" s="29"/>
+      <c r="B137" s="24"/>
+      <c r="C137" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D137" s="28" t="s">
         <v>274</v>
       </c>
-      <c r="D125" s="4" t="s">
+      <c r="E137" s="9"/>
+    </row>
+    <row r="138" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A138" s="29"/>
+      <c r="B138" s="24"/>
+      <c r="C138" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D138" s="28" t="s">
         <v>275</v>
       </c>
-      <c r="E125" s="4"/>
-    </row>
-    <row r="126" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A126" s="14"/>
-      <c r="B126" s="14"/>
-      <c r="C126" s="4" t="s">
+      <c r="E138" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="139" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A139" s="29"/>
+      <c r="B139" s="24" t="s">
         <v>276</v>
       </c>
-      <c r="D126" s="4" t="s">
+      <c r="C139" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D139" s="28" t="s">
         <v>277</v>
       </c>
-      <c r="E126" s="4"/>
-    </row>
-    <row r="127" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A127" s="14"/>
-      <c r="B127" s="14"/>
-      <c r="C127" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D127" s="4" t="s">
+      <c r="E139" s="9"/>
+    </row>
+    <row r="140" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A140" s="29"/>
+      <c r="B140" s="24"/>
+      <c r="C140" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D140" s="28" t="s">
         <v>278</v>
       </c>
-      <c r="E127" s="4"/>
-    </row>
-    <row r="128" s="1" customFormat="1" ht="27.75" customHeight="1" spans="1:5">
-      <c r="A128" s="14"/>
-      <c r="B128" s="14"/>
-      <c r="C128" s="4" t="s">
+      <c r="E140" s="9"/>
+    </row>
+    <row r="141" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A141" s="29"/>
+      <c r="B141" s="24"/>
+      <c r="C141" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D141" s="28" t="s">
         <v>279</v>
       </c>
-      <c r="D128" s="4" t="s">
+      <c r="E141" s="9"/>
+    </row>
+    <row r="142" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A142" s="29"/>
+      <c r="B142" s="24"/>
+      <c r="C142" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D142" s="28" t="s">
         <v>280</v>
       </c>
-      <c r="E128" s="21" t="s">
+      <c r="E142" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="143" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A143" s="30"/>
+      <c r="B143" s="11"/>
+      <c r="C143" s="11"/>
+      <c r="D143" s="11"/>
+      <c r="E143" s="11"/>
+    </row>
+    <row r="144" s="1" customFormat="1" ht="27.75" customHeight="1" spans="1:5">
+      <c r="A144" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="129" s="1" customFormat="1" ht="27.75" customHeight="1" spans="1:5">
-      <c r="A129" s="14"/>
-      <c r="B129" s="14"/>
-      <c r="C129" s="4" t="s">
+      <c r="B144" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="D129" s="4" t="s">
+      <c r="C144" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D144" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="E129" s="21" t="s">
+      <c r="E144" s="21" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="130" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A130" s="14"/>
-      <c r="B130" s="14"/>
-      <c r="C130" s="4" t="s">
+    <row r="145" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A145" s="14"/>
+      <c r="B145" s="14"/>
+      <c r="C145" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D145" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="D130" s="4" t="s">
+      <c r="E145" s="4"/>
+    </row>
+    <row r="146" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A146" s="14"/>
+      <c r="B146" s="14"/>
+      <c r="C146" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="E130" s="4" t="s">
+      <c r="D146" s="4" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="131" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A131" s="14"/>
-      <c r="B131" s="14"/>
-      <c r="C131" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D131" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="E131" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="132" s="1" customFormat="1" ht="41.25" customHeight="1" spans="1:5">
-      <c r="A132" s="14"/>
-      <c r="B132" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="D132" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="E132" s="21" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="133" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A133" s="14"/>
-      <c r="B133" s="14"/>
-      <c r="C133" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="E133" s="4" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="134" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A134" s="14"/>
-      <c r="B134" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="E134" s="4" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="135" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A135" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D135" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="E135" s="4" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="136" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A136" s="14"/>
-      <c r="B136" s="14"/>
-      <c r="C136" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D136" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="E136" s="4"/>
-    </row>
-    <row r="137" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A137" s="14"/>
-      <c r="B137" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="D137" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="E137" s="4" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="138" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A138" s="14"/>
-      <c r="B138" s="14"/>
-      <c r="C138" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D138" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E138" s="4"/>
-    </row>
-    <row r="139" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A139" s="14"/>
-      <c r="B139" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="D139" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="E139" s="4" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="140" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A140" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="B140" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D140" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="E140" s="21" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="141" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A141" s="14"/>
-      <c r="B141" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="D141" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="E141" s="14"/>
-    </row>
-    <row r="142" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A142" s="14"/>
-      <c r="B142" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="D142" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="E142" s="14"/>
-    </row>
-    <row r="143" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A143" s="14"/>
-      <c r="B143" s="18" t="s">
-        <v>317</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="D143" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E143" s="4" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="144" s="1" customFormat="1" ht="27.75" customHeight="1" spans="1:5">
-      <c r="A144" s="14"/>
-      <c r="B144" s="20"/>
-      <c r="C144" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="D144" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="E144" s="21" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="145" s="1" customFormat="1" ht="27.75" customHeight="1" spans="1:5">
-      <c r="A145" s="14"/>
-      <c r="B145" s="20"/>
-      <c r="C145" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="D145" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="E145" s="21" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="146" s="1" customFormat="1" ht="27.75" customHeight="1" spans="1:5">
-      <c r="A146" s="14"/>
-      <c r="B146" s="20"/>
-      <c r="C146" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="D146" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="E146" s="21" t="s">
-        <v>328</v>
-      </c>
+      <c r="E146" s="4"/>
     </row>
     <row r="147" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A147" s="14"/>
-      <c r="B147" s="20"/>
+      <c r="B147" s="14"/>
       <c r="C147" s="4" t="s">
-        <v>329</v>
+        <v>288</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="E147" s="4" t="s">
-        <v>331</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="E147" s="4"/>
     </row>
     <row r="148" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A148" s="14"/>
-      <c r="B148" s="20"/>
+      <c r="B148" s="14"/>
       <c r="C148" s="4" t="s">
-        <v>332</v>
+        <v>290</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="E148" s="4" t="s">
-        <v>334</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="E148" s="4"/>
     </row>
     <row r="149" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A149" s="14"/>
-      <c r="B149" s="19"/>
+      <c r="B149" s="14"/>
       <c r="C149" s="4" t="s">
-        <v>335</v>
+        <v>292</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="E149" s="4" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="150" s="1" customFormat="1" ht="68.25" customHeight="1" spans="1:5">
+        <v>293</v>
+      </c>
+      <c r="E149" s="4"/>
+    </row>
+    <row r="150" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A150" s="14"/>
-      <c r="B150" s="4" t="s">
-        <v>48</v>
-      </c>
+      <c r="B150" s="14"/>
       <c r="C150" s="4" t="s">
-        <v>34</v>
+        <v>294</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="E150" s="21" t="s">
-        <v>339</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="E150" s="4"/>
     </row>
     <row r="151" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A151" s="14"/>
-      <c r="B151" s="4" t="s">
-        <v>340</v>
-      </c>
+      <c r="B151" s="14"/>
       <c r="C151" s="4" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="E151" s="4" t="s">
-        <v>342</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="E151" s="4"/>
     </row>
     <row r="152" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A152" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>344</v>
-      </c>
+      <c r="A152" s="14"/>
+      <c r="B152" s="14"/>
       <c r="C152" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="E152" s="4" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="153" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A153" s="24"/>
-      <c r="B153" s="11"/>
-      <c r="C153" s="11"/>
-      <c r="D153" s="11"/>
-      <c r="E153" s="11"/>
-    </row>
-    <row r="154" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A154" s="18" t="s">
-        <v>347</v>
-      </c>
-      <c r="B154" s="4" t="s">
-        <v>348</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="E152" s="4"/>
+    </row>
+    <row r="153" s="1" customFormat="1" ht="27.75" customHeight="1" spans="1:5">
+      <c r="A153" s="14"/>
+      <c r="B153" s="14"/>
+      <c r="C153" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="E153" s="21" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="154" s="1" customFormat="1" ht="27.75" customHeight="1" spans="1:5">
+      <c r="A154" s="14"/>
+      <c r="B154" s="14"/>
       <c r="C154" s="4" t="s">
-        <v>349</v>
+        <v>302</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="E154" s="4" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="155" s="1" customFormat="1" ht="68.25" customHeight="1" spans="1:5">
-      <c r="A155" s="20"/>
+        <v>303</v>
+      </c>
+      <c r="E154" s="21" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="155" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A155" s="14"/>
       <c r="B155" s="14"/>
       <c r="C155" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="E155" s="4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="156" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A156" s="14"/>
+      <c r="B156" s="14"/>
+      <c r="C156" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="E156" s="4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="157" s="1" customFormat="1" ht="41.25" customHeight="1" spans="1:5">
+      <c r="A157" s="14"/>
+      <c r="B157" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="E157" s="21" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="158" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A158" s="14"/>
+      <c r="B158" s="14"/>
+      <c r="C158" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="E158" s="4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="159" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A159" s="14"/>
+      <c r="B159" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="E159" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="160" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A160" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="E160" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="161" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A161" s="14"/>
+      <c r="B161" s="14"/>
+      <c r="C161" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="E161" s="4"/>
+    </row>
+    <row r="162" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A162" s="14"/>
+      <c r="B162" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E162" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="163" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A163" s="14"/>
+      <c r="B163" s="14"/>
+      <c r="C163" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="E163" s="4"/>
+    </row>
+    <row r="164" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A164" s="14"/>
+      <c r="B164" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="E164" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="165" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A165" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="E165" s="21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="166" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A166" s="14"/>
+      <c r="B166" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="E166" s="14"/>
+    </row>
+    <row r="167" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A167" s="14"/>
+      <c r="B167" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="E167" s="14"/>
+    </row>
+    <row r="168" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A168" s="14"/>
+      <c r="B168" s="18" t="s">
+        <v>337</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E168" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="169" s="1" customFormat="1" ht="27.75" customHeight="1" spans="1:5">
+      <c r="A169" s="14"/>
+      <c r="B169" s="20"/>
+      <c r="C169" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="E169" s="21" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="170" s="1" customFormat="1" ht="27.75" customHeight="1" spans="1:5">
+      <c r="A170" s="14"/>
+      <c r="B170" s="20"/>
+      <c r="C170" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="E170" s="21" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="171" s="1" customFormat="1" ht="27.75" customHeight="1" spans="1:5">
+      <c r="A171" s="14"/>
+      <c r="B171" s="20"/>
+      <c r="C171" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="E171" s="21" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="172" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A172" s="14"/>
+      <c r="B172" s="20"/>
+      <c r="C172" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="E172" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="173" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A173" s="14"/>
+      <c r="B173" s="20"/>
+      <c r="C173" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="D155" s="4" t="s">
+      <c r="D173" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="E155" s="21" t="s">
+      <c r="E173" s="4" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="156" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A156" s="20"/>
-      <c r="B156" s="4" t="s">
+    <row r="174" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A174" s="14"/>
+      <c r="B174" s="19"/>
+      <c r="C174" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="C156" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="D156" s="4" t="s">
+      <c r="D174" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="E156" s="4" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="157" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A157" s="20"/>
-      <c r="B157" s="18" t="s">
+      <c r="E174" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="C157" s="4" t="s">
+    </row>
+    <row r="175" s="1" customFormat="1" ht="68.25" customHeight="1" spans="1:5">
+      <c r="A175" s="14"/>
+      <c r="B175" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D157" s="4" t="s">
+      <c r="C175" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D175" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="E157" s="4" t="s">
+      <c r="E175" s="21" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="158" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A158" s="20"/>
-      <c r="B158" s="20"/>
-      <c r="C158" s="4" t="s">
+    <row r="176" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A176" s="14"/>
+      <c r="B176" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="D158" s="4" t="s">
+      <c r="C176" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D176" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="E158" s="4" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="159" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A159" s="20"/>
-      <c r="B159" s="19"/>
-      <c r="C159" s="4" t="s">
+      <c r="E176" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="D159" s="4" t="s">
+    </row>
+    <row r="177" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A177" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="E159" s="4" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="160" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A160" s="20"/>
-      <c r="B160" s="4" t="s">
+      <c r="B177" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="C160" s="4" t="s">
+      <c r="C177" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D177" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="D160" s="4" t="s">
+      <c r="E177" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="E160" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="161" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A161" s="20"/>
-      <c r="B161" s="4" t="s">
+    </row>
+    <row r="178" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A178" s="30"/>
+      <c r="B178" s="11"/>
+      <c r="C178" s="11"/>
+      <c r="D178" s="11"/>
+      <c r="E178" s="11"/>
+    </row>
+    <row r="179" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A179" s="18" t="s">
         <v>367</v>
       </c>
-      <c r="C161" s="4" t="s">
+      <c r="B179" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="E179" s="4" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="180" s="1" customFormat="1" ht="68.25" customHeight="1" spans="1:5">
+      <c r="A180" s="20"/>
+      <c r="B180" s="14"/>
+      <c r="C180" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="E180" s="21" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="181" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A181" s="20"/>
+      <c r="B181" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="E181" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="182" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A182" s="20"/>
+      <c r="B182" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="E182" s="4" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="183" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A183" s="20"/>
+      <c r="B183" s="20"/>
+      <c r="C183" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="E183" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="184" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A184" s="20"/>
+      <c r="B184" s="19"/>
+      <c r="C184" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="E184" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="185" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A185" s="20"/>
+      <c r="B185" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="E185" s="4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="186" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A186" s="20"/>
+      <c r="B186" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="C186" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D161" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="E161" s="4" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="162" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A162" s="20"/>
-      <c r="B162" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="D162" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="E162" s="4" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="163" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A163" s="20"/>
-      <c r="B163" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="C163" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="D163" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="E163" s="4" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="164" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A164" s="20"/>
-      <c r="B164" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="C164" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="D164" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="E164" s="4" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="165" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A165" s="18" t="s">
-        <v>380</v>
-      </c>
-      <c r="B165" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="C165" s="4" t="s">
+      <c r="D186" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="E186" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="187" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A187" s="20"/>
+      <c r="B187" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="E187" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="188" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A188" s="20"/>
+      <c r="B188" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="E188" s="4" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="189" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A189" s="20"/>
+      <c r="B189" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="E189" s="4" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="190" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A190" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C190" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D165" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="E165" s="4" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="166" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A166" s="18"/>
-      <c r="B166" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="C166" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="D166" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="E166" s="4" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="167" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A167" s="20"/>
-      <c r="B167" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="C167" s="4"/>
-      <c r="D167" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="E167" s="4" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="168" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A168" s="19"/>
-      <c r="B168" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="C168" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="D168" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="E168" s="4" t="s">
-        <v>376</v>
+      <c r="D190" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="E190" s="4" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="191" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A191" s="18"/>
+      <c r="B191" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="E191" s="4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="192" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A192" s="20"/>
+      <c r="B192" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C192" s="4"/>
+      <c r="D192" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="E192" s="4" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="193" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A193" s="19"/>
+      <c r="B193" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="E193" s="4" t="s">
+        <v>396</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="55">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A86:E86"/>
-    <mergeCell ref="A118:E118"/>
-    <mergeCell ref="A153:E153"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A143:E143"/>
+    <mergeCell ref="A178:E178"/>
     <mergeCell ref="A3:A13"/>
     <mergeCell ref="A15:A21"/>
     <mergeCell ref="A22:A35"/>
-    <mergeCell ref="A37:A59"/>
-    <mergeCell ref="A61:A85"/>
-    <mergeCell ref="A87:A96"/>
-    <mergeCell ref="A97:A99"/>
-    <mergeCell ref="A100:A106"/>
-    <mergeCell ref="A107:A117"/>
-    <mergeCell ref="A119:A134"/>
-    <mergeCell ref="A135:A139"/>
-    <mergeCell ref="A140:A151"/>
-    <mergeCell ref="A154:A164"/>
-    <mergeCell ref="A165:A168"/>
+    <mergeCell ref="A37:A67"/>
+    <mergeCell ref="A69:A93"/>
+    <mergeCell ref="A95:A104"/>
+    <mergeCell ref="A105:A107"/>
+    <mergeCell ref="A108:A114"/>
+    <mergeCell ref="A115:A125"/>
+    <mergeCell ref="A126:A142"/>
+    <mergeCell ref="A144:A159"/>
+    <mergeCell ref="A160:A164"/>
+    <mergeCell ref="A165:A176"/>
+    <mergeCell ref="A179:A189"/>
+    <mergeCell ref="A190:A193"/>
     <mergeCell ref="B37:B42"/>
     <mergeCell ref="B44:B47"/>
     <mergeCell ref="B48:B51"/>
     <mergeCell ref="B52:B55"/>
     <mergeCell ref="B56:B59"/>
-    <mergeCell ref="B61:B64"/>
-    <mergeCell ref="B66:B69"/>
-    <mergeCell ref="B70:B74"/>
-    <mergeCell ref="B75:B79"/>
-    <mergeCell ref="B80:B83"/>
+    <mergeCell ref="B60:B63"/>
+    <mergeCell ref="B64:B67"/>
+    <mergeCell ref="B69:B72"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="B78:B82"/>
+    <mergeCell ref="B83:B87"/>
     <mergeCell ref="B88:B91"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="B114:B117"/>
-    <mergeCell ref="B119:B131"/>
-    <mergeCell ref="B132:B133"/>
-    <mergeCell ref="B135:B136"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="B143:B149"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="B157:B159"/>
+    <mergeCell ref="B96:B99"/>
+    <mergeCell ref="B115:B117"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="B122:B125"/>
+    <mergeCell ref="B127:B130"/>
+    <mergeCell ref="B131:B134"/>
+    <mergeCell ref="B135:B138"/>
+    <mergeCell ref="B139:B142"/>
+    <mergeCell ref="B144:B156"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="B168:B174"/>
+    <mergeCell ref="B179:B180"/>
+    <mergeCell ref="B182:B184"/>
     <mergeCell ref="E18:E19"/>
     <mergeCell ref="E25:E26"/>
-    <mergeCell ref="E101:E106"/>
-    <mergeCell ref="E140:E142"/>
+    <mergeCell ref="E109:E114"/>
+    <mergeCell ref="E165:E167"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -6249,23 +6642,23 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="16.5" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="19.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.1333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="33.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="80.3666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.1363636363636" style="1" customWidth="1"/>
+    <col min="3" max="3" width="33.3727272727273" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.2545454545455" style="1" customWidth="1"/>
+    <col min="5" max="5" width="80.3636363636364" style="1" customWidth="1"/>
     <col min="6" max="16384" width="10" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A1" s="4"/>
       <c r="B1" s="4" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>3</v>
@@ -6283,13 +6676,13 @@
         <v>32</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>47</v>
@@ -6298,13 +6691,13 @@
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A4" s="19"/>
       <c r="B4" s="4" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>50</v>
@@ -6315,13 +6708,13 @@
         <v>51</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>72</v>
@@ -6330,13 +6723,13 @@
     <row r="6" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A6" s="20"/>
       <c r="B6" s="4" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>61</v>
@@ -6345,31 +6738,31 @@
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A7" s="20"/>
       <c r="B7" s="4" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="27.75" customHeight="1" spans="1:5">
       <c r="A8" s="19"/>
       <c r="B8" s="4" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:5">
@@ -6378,10 +6771,10 @@
         <v>79</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>81</v>
@@ -6393,10 +6786,10 @@
         <v>82</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="E10" s="21" t="s">
         <v>84</v>
@@ -6417,13 +6810,13 @@
         <v>48</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:5">
@@ -6432,13 +6825,13 @@
         <v>106</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>417</v>
+        <v>437</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:5">
@@ -6447,176 +6840,176 @@
         <v>115</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A15" s="20"/>
       <c r="B15" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="E15" s="4"/>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A16" s="20"/>
       <c r="B16" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="E16" s="4"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="54.75" customHeight="1" spans="1:5">
       <c r="A17" s="18" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>424</v>
+        <v>444</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="41.25" customHeight="1" spans="1:5">
       <c r="A18" s="20"/>
       <c r="B18" s="4" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>428</v>
+        <v>448</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A19" s="20"/>
       <c r="B19" s="4" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A20" s="20"/>
       <c r="B20" s="4" t="s">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A21" s="20"/>
       <c r="B21" s="4" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A22" s="20"/>
       <c r="B22" s="4" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A23" s="20"/>
       <c r="B23" s="4" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>444</v>
+        <v>464</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A24" s="20"/>
       <c r="B24" s="4" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A25" s="20"/>
       <c r="B25" s="4" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:5">
@@ -6628,307 +7021,307 @@
     </row>
     <row r="27" s="1" customFormat="1" ht="108.75" customHeight="1" spans="1:5">
       <c r="A27" s="18" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A28" s="20"/>
       <c r="B28" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A29" s="20"/>
       <c r="B29" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A30" s="20"/>
       <c r="B30" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A31" s="20"/>
       <c r="B31" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="E31" s="20"/>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A32" s="20"/>
       <c r="B32" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="E32" s="20"/>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A33" s="19"/>
       <c r="B33" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="E33" s="19"/>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A34" s="18" t="s">
-        <v>463</v>
+        <v>483</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A35" s="20"/>
       <c r="B35" s="4" t="s">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>469</v>
+        <v>489</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A36" s="19"/>
       <c r="B36" s="4" t="s">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="E36" s="19"/>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A37" s="18" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" ht="20.5" customHeight="1" spans="1:5">
       <c r="A38" s="20"/>
       <c r="B38" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" ht="19.75" customHeight="1" spans="1:5">
       <c r="A39" s="20"/>
       <c r="B39" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>476</v>
+        <v>496</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="E39" s="20"/>
     </row>
     <row r="40" s="1" customFormat="1" ht="20.75" customHeight="1" spans="1:5">
       <c r="A40" s="20"/>
       <c r="B40" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="E40" s="20"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="22.75" customHeight="1" spans="1:5">
       <c r="A41" s="20"/>
       <c r="B41" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="E41" s="20"/>
     </row>
     <row r="42" s="1" customFormat="1" ht="19.75" customHeight="1" spans="1:5">
       <c r="A42" s="20"/>
       <c r="B42" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>479</v>
+        <v>499</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="E42" s="20"/>
     </row>
     <row r="43" s="1" customFormat="1" ht="19.75" customHeight="1" spans="1:5">
       <c r="A43" s="19"/>
       <c r="B43" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="E43" s="19"/>
     </row>
     <row r="44" s="1" customFormat="1" ht="41.25" customHeight="1" spans="1:5">
       <c r="A44" s="18" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>481</v>
+        <v>501</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>484</v>
+        <v>504</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" ht="27.75" customHeight="1" spans="1:5">
       <c r="A45" s="20"/>
       <c r="B45" s="4" t="s">
-        <v>485</v>
+        <v>505</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>486</v>
+        <v>506</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="E45" s="21" t="s">
-        <v>488</v>
+        <v>508</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A46" s="20"/>
       <c r="B46" s="4" t="s">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>492</v>
+        <v>512</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" ht="27.75" customHeight="1" spans="1:5">
       <c r="A47" s="19"/>
       <c r="B47" s="4" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>494</v>
+        <v>514</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="E47" s="21" t="s">
-        <v>496</v>
+        <v>516</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:5">
@@ -6940,205 +7333,205 @@
     </row>
     <row r="49" s="1" customFormat="1" ht="27.75" customHeight="1" spans="1:5">
       <c r="A49" s="18" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>497</v>
+        <v>517</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" ht="68.25" customHeight="1" spans="1:5">
       <c r="A50" s="20"/>
       <c r="B50" s="4" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>502</v>
+        <v>522</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>504</v>
+        <v>524</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A51" s="19"/>
       <c r="B51" s="4" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" ht="41.25" customHeight="1" spans="1:5">
       <c r="A52" s="18" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>48</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>507</v>
+        <v>527</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A53" s="20"/>
       <c r="B53" s="4" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>508</v>
+        <v>528</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>509</v>
+        <v>529</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A54" s="20"/>
       <c r="B54" s="4" t="s">
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>512</v>
+        <v>532</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" ht="27.75" customHeight="1" spans="1:5">
       <c r="A55" s="20"/>
       <c r="B55" s="4" t="s">
-        <v>513</v>
+        <v>533</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>514</v>
+        <v>534</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="E55" s="21" t="s">
-        <v>516</v>
+        <v>536</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A56" s="19"/>
       <c r="B56" s="4" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A57" s="18" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>519</v>
+        <v>539</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>522</v>
+        <v>542</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" ht="68.25" customHeight="1" spans="1:5">
       <c r="A58" s="20"/>
       <c r="B58" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E58" s="21" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" ht="41.25" customHeight="1" spans="1:5">
       <c r="A59" s="20"/>
       <c r="B59" s="4" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>527</v>
+        <v>547</v>
       </c>
       <c r="E59" s="21" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A60" s="19"/>
       <c r="B60" s="4" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>531</v>
+        <v>551</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A61" s="4" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>532</v>
+        <v>552</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>533</v>
+        <v>553</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="1:5">
@@ -7150,186 +7543,186 @@
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A63" s="18" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>535</v>
+        <v>555</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" ht="54.75" customHeight="1" spans="1:5">
       <c r="A64" s="20"/>
       <c r="B64" s="4" t="s">
-        <v>536</v>
+        <v>556</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>537</v>
+        <v>557</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="E64" s="21" t="s">
-        <v>539</v>
+        <v>559</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A65" s="20"/>
       <c r="B65" s="4" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>541</v>
+        <v>561</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" ht="41.25" customHeight="1" spans="1:5">
       <c r="A66" s="20"/>
       <c r="B66" s="4" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>542</v>
+        <v>562</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>543</v>
+        <v>563</v>
       </c>
       <c r="E66" s="21" t="s">
-        <v>544</v>
+        <v>564</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A67" s="20"/>
       <c r="B67" s="4" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>545</v>
+        <v>565</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>541</v>
+        <v>561</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A68" s="20"/>
       <c r="B68" s="4" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>546</v>
+        <v>566</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>541</v>
+        <v>561</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A69" s="20"/>
       <c r="B69" s="4" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>547</v>
+        <v>567</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>541</v>
+        <v>561</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A70" s="20"/>
       <c r="B70" s="4" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>548</v>
+        <v>568</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>549</v>
+        <v>569</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A71" s="18" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>551</v>
+        <v>571</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A72" s="18"/>
       <c r="B72" s="4" t="s">
-        <v>552</v>
+        <v>572</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>553</v>
+        <v>573</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>541</v>
+        <v>561</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A73" s="18"/>
       <c r="B73" s="4" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>554</v>
+        <v>574</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>551</v>
+        <v>571</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A74" s="19"/>
       <c r="B74" s="4" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>555</v>
+        <v>575</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>541</v>
+        <v>561</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="1:5">
@@ -7341,64 +7734,64 @@
     </row>
     <row r="76" s="1" customFormat="1" ht="41.25" customHeight="1" spans="1:5">
       <c r="A76" s="18" t="s">
-        <v>556</v>
+        <v>576</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>557</v>
+        <v>577</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>558</v>
+        <v>578</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>559</v>
+        <v>579</v>
       </c>
       <c r="E76" s="21" t="s">
-        <v>560</v>
+        <v>580</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" ht="162.75" customHeight="1" spans="1:5">
       <c r="A77" s="20"/>
       <c r="B77" s="4" t="s">
-        <v>561</v>
+        <v>581</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>562</v>
+        <v>582</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>563</v>
+        <v>583</v>
       </c>
       <c r="E77" s="21" t="s">
-        <v>564</v>
+        <v>584</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" ht="41.25" customHeight="1" spans="1:5">
       <c r="A78" s="20"/>
       <c r="B78" s="4" t="s">
-        <v>565</v>
+        <v>585</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>566</v>
+        <v>586</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>567</v>
+        <v>587</v>
       </c>
       <c r="E78" s="21" t="s">
-        <v>568</v>
+        <v>588</v>
       </c>
     </row>
     <row r="79" s="1" customFormat="1" ht="81.75" customHeight="1" spans="1:5">
       <c r="A79" s="19"/>
       <c r="B79" s="4" t="s">
-        <v>569</v>
+        <v>589</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>570</v>
+        <v>590</v>
       </c>
       <c r="D79" s="21" t="s">
-        <v>571</v>
+        <v>591</v>
       </c>
       <c r="E79" s="21" t="s">
-        <v>572</v>
+        <v>592</v>
       </c>
     </row>
   </sheetData>
@@ -7440,102 +7833,90 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" style="1"/>
-    <col min="2" max="2" width="11.3666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3636363636364" style="1" customWidth="1"/>
     <col min="3" max="7" width="10" style="1"/>
-    <col min="8" max="8" width="12.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6272727272727" style="1" customWidth="1"/>
     <col min="9" max="10" width="10" style="1"/>
-    <col min="11" max="11" width="13.25" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.2545454545455" style="1" customWidth="1"/>
     <col min="12" max="16384" width="10" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="18" customHeight="1"/>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A2" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B2" s="3"/>
-      <c r="C2" s="1"/>
       <c r="D2" s="2" t="s">
-        <v>573</v>
+        <v>593</v>
       </c>
       <c r="E2" s="3"/>
-      <c r="F2" s="1"/>
       <c r="G2" s="2" t="s">
-        <v>574</v>
+        <v>594</v>
       </c>
       <c r="H2" s="3"/>
-      <c r="I2" s="1"/>
       <c r="J2" s="2" t="s">
-        <v>575</v>
+        <v>595</v>
       </c>
       <c r="K2" s="3"/>
-      <c r="L2" s="1"/>
       <c r="M2" s="2" t="s">
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="N2" s="3"/>
-      <c r="O2" s="1"/>
       <c r="P2" s="2" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="Q2" s="11"/>
       <c r="R2" s="11"/>
-      <c r="S2" s="1"/>
       <c r="T2" s="2" t="s">
-        <v>577</v>
+        <v>597</v>
       </c>
       <c r="U2" s="11"/>
       <c r="V2" s="11"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A3" s="4" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="C3" s="1"/>
+        <v>599</v>
+      </c>
       <c r="D3" s="4" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="F3" s="1"/>
+        <v>599</v>
+      </c>
       <c r="G3" s="4" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="I3" s="1"/>
+        <v>165</v>
+      </c>
       <c r="J3" s="4" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="L3" s="1"/>
+        <v>599</v>
+      </c>
       <c r="M3" s="10" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>579</v>
-      </c>
-      <c r="O3" s="1"/>
+        <v>599</v>
+      </c>
       <c r="P3" s="4" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="R3" s="13"/>
-      <c r="S3" s="1"/>
       <c r="T3" s="4" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="U3" s="12" t="s">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="V3" s="13"/>
     </row>
@@ -7544,50 +7925,44 @@
         <v>18</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="C4" s="1"/>
+        <v>601</v>
+      </c>
       <c r="D4" s="5">
         <v>19</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>582</v>
-      </c>
-      <c r="F4" s="1"/>
+        <v>602</v>
+      </c>
       <c r="G4" s="4">
         <v>12</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="I4" s="1"/>
+        <v>603</v>
+      </c>
       <c r="J4" s="4">
         <v>0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="L4" s="1"/>
+        <v>604</v>
+      </c>
       <c r="M4" s="10">
         <v>0</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>585</v>
-      </c>
-      <c r="O4" s="1"/>
+        <v>605</v>
+      </c>
       <c r="P4" s="4">
         <v>0</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="R4" s="13"/>
-      <c r="S4" s="1"/>
       <c r="T4" s="4">
         <v>32</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>587</v>
+        <v>607</v>
       </c>
       <c r="V4" s="13"/>
     </row>
@@ -7596,50 +7971,44 @@
         <v>17</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>588</v>
-      </c>
-      <c r="C5" s="1"/>
+        <v>608</v>
+      </c>
       <c r="D5" s="5">
         <v>18</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>589</v>
-      </c>
-      <c r="F5" s="1"/>
+        <v>609</v>
+      </c>
       <c r="G5" s="4">
         <v>11</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>590</v>
-      </c>
-      <c r="I5" s="1"/>
+        <v>610</v>
+      </c>
       <c r="J5" s="4">
         <v>1</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="L5" s="1"/>
+        <v>611</v>
+      </c>
       <c r="M5" s="10">
         <v>1</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>592</v>
-      </c>
-      <c r="O5" s="1"/>
+        <v>612</v>
+      </c>
       <c r="P5" s="4">
         <v>1</v>
       </c>
       <c r="Q5" s="12" t="s">
-        <v>593</v>
+        <v>613</v>
       </c>
       <c r="R5" s="13"/>
-      <c r="S5" s="1"/>
       <c r="T5" s="4">
         <v>33</v>
       </c>
       <c r="U5" s="12" t="s">
-        <v>594</v>
+        <v>614</v>
       </c>
       <c r="V5" s="13"/>
     </row>
@@ -7648,50 +8017,44 @@
         <v>16</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>595</v>
-      </c>
-      <c r="C6" s="1"/>
+        <v>615</v>
+      </c>
       <c r="D6" s="5">
         <v>17</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="F6" s="1"/>
+        <v>616</v>
+      </c>
       <c r="G6" s="4">
         <v>10</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="I6" s="1"/>
+        <v>617</v>
+      </c>
       <c r="J6" s="4">
         <v>2</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>598</v>
-      </c>
-      <c r="L6" s="1"/>
+        <v>618</v>
+      </c>
       <c r="M6" s="10">
         <v>2</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>599</v>
-      </c>
-      <c r="O6" s="1"/>
+        <v>619</v>
+      </c>
       <c r="P6" s="4">
         <v>2</v>
       </c>
       <c r="Q6" s="12" t="s">
-        <v>594</v>
+        <v>614</v>
       </c>
       <c r="R6" s="13"/>
-      <c r="S6" s="1"/>
       <c r="T6" s="4">
         <v>34</v>
       </c>
       <c r="U6" s="12" t="s">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="V6" s="13"/>
     </row>
@@ -7700,50 +8063,44 @@
         <v>15</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="C7" s="1"/>
+        <v>621</v>
+      </c>
       <c r="D7" s="5">
         <v>16</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>602</v>
-      </c>
-      <c r="F7" s="1"/>
+        <v>622</v>
+      </c>
       <c r="G7" s="4" t="s">
-        <v>603</v>
+        <v>623</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="I7" s="1"/>
+        <v>624</v>
+      </c>
       <c r="J7" s="4">
         <v>3</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>605</v>
-      </c>
-      <c r="L7" s="1"/>
+        <v>625</v>
+      </c>
       <c r="M7" s="10">
         <v>3</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>606</v>
-      </c>
-      <c r="O7" s="1"/>
+        <v>626</v>
+      </c>
       <c r="P7" s="4">
         <v>3</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="R7" s="13"/>
-      <c r="S7" s="1"/>
       <c r="T7" s="4">
         <v>31</v>
       </c>
       <c r="U7" s="12" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="V7" s="13"/>
     </row>
@@ -7752,50 +8109,44 @@
         <v>14</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>608</v>
-      </c>
-      <c r="C8" s="1"/>
+        <v>628</v>
+      </c>
       <c r="D8" s="5">
         <v>15</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>609</v>
-      </c>
-      <c r="F8" s="1"/>
+        <v>629</v>
+      </c>
       <c r="G8" s="4" t="s">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>611</v>
-      </c>
-      <c r="I8" s="1"/>
+        <v>631</v>
+      </c>
       <c r="J8" s="4">
         <v>4</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="L8" s="1"/>
+        <v>632</v>
+      </c>
       <c r="M8" s="10">
         <v>4</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>613</v>
-      </c>
-      <c r="O8" s="1"/>
+        <v>633</v>
+      </c>
       <c r="P8" s="4">
         <v>4</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="R8" s="13"/>
-      <c r="S8" s="1"/>
       <c r="T8" s="4">
         <v>16</v>
       </c>
       <c r="U8" s="12" t="s">
-        <v>614</v>
+        <v>634</v>
       </c>
       <c r="V8" s="13"/>
     </row>
@@ -7804,50 +8155,44 @@
         <v>13</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>615</v>
-      </c>
-      <c r="C9" s="1"/>
+        <v>635</v>
+      </c>
       <c r="D9" s="5">
         <v>14</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>616</v>
-      </c>
-      <c r="F9" s="1"/>
+        <v>636</v>
+      </c>
       <c r="G9" s="4" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="I9" s="1"/>
+        <v>638</v>
+      </c>
       <c r="J9" s="4">
         <v>5</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>619</v>
-      </c>
-      <c r="L9" s="1"/>
+        <v>639</v>
+      </c>
       <c r="M9" s="10">
         <v>5</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>620</v>
-      </c>
-      <c r="O9" s="1"/>
+        <v>640</v>
+      </c>
       <c r="P9" s="4">
         <v>5</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>614</v>
+        <v>634</v>
       </c>
       <c r="R9" s="13"/>
-      <c r="S9" s="1"/>
       <c r="T9" s="4">
         <v>93</v>
       </c>
       <c r="U9" s="12" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="V9" s="13"/>
     </row>
@@ -7856,50 +8201,44 @@
         <v>12</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="C10" s="1"/>
+        <v>642</v>
+      </c>
       <c r="D10" s="5">
         <v>13</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>623</v>
-      </c>
-      <c r="F10" s="1"/>
+        <v>643</v>
+      </c>
       <c r="G10" s="4" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>625</v>
-      </c>
-      <c r="I10" s="1"/>
+        <v>645</v>
+      </c>
       <c r="J10" s="4">
         <v>6</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>626</v>
-      </c>
-      <c r="L10" s="1"/>
+        <v>646</v>
+      </c>
       <c r="M10" s="10">
         <v>6</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>627</v>
-      </c>
-      <c r="O10" s="1"/>
+        <v>647</v>
+      </c>
       <c r="P10" s="4">
         <v>6</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>628</v>
+        <v>648</v>
       </c>
       <c r="R10" s="13"/>
-      <c r="S10" s="1"/>
       <c r="T10" s="4">
         <v>94</v>
       </c>
       <c r="U10" s="12" t="s">
-        <v>629</v>
+        <v>649</v>
       </c>
       <c r="V10" s="13"/>
     </row>
@@ -7908,50 +8247,44 @@
         <v>11</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>630</v>
-      </c>
-      <c r="C11" s="1"/>
+        <v>650</v>
+      </c>
       <c r="D11" s="5">
         <v>12</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>631</v>
-      </c>
-      <c r="F11" s="1"/>
+        <v>651</v>
+      </c>
       <c r="G11" s="4" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>633</v>
-      </c>
-      <c r="I11" s="1"/>
+        <v>653</v>
+      </c>
       <c r="J11" s="4">
         <v>7</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>634</v>
-      </c>
-      <c r="L11" s="1"/>
+        <v>654</v>
+      </c>
       <c r="M11" s="10">
         <v>7</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>635</v>
-      </c>
-      <c r="O11" s="1"/>
+        <v>655</v>
+      </c>
       <c r="P11" s="4">
         <v>7</v>
       </c>
       <c r="Q11" s="12" t="s">
-        <v>636</v>
+        <v>656</v>
       </c>
       <c r="R11" s="13"/>
-      <c r="S11" s="1"/>
       <c r="T11" s="4">
         <v>95</v>
       </c>
       <c r="U11" s="12" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="V11" s="13"/>
     </row>
@@ -7960,299 +8293,265 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>638</v>
-      </c>
-      <c r="C12" s="1"/>
+        <v>658</v>
+      </c>
       <c r="D12" s="5">
         <v>11</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>639</v>
-      </c>
-      <c r="F12" s="1"/>
+        <v>659</v>
+      </c>
       <c r="G12" s="4" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>641</v>
-      </c>
-      <c r="I12" s="1"/>
+        <v>661</v>
+      </c>
       <c r="J12" s="4">
         <v>8</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="L12" s="1"/>
+        <v>662</v>
+      </c>
       <c r="M12" s="10">
         <v>8</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>643</v>
-      </c>
-      <c r="O12" s="1"/>
+        <v>663</v>
+      </c>
       <c r="P12" s="4">
         <v>8</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>629</v>
+        <v>649</v>
       </c>
       <c r="R12" s="13"/>
-      <c r="S12" s="1"/>
       <c r="T12" s="4">
         <v>96</v>
       </c>
       <c r="U12" s="12" t="s">
-        <v>644</v>
+        <v>664</v>
       </c>
       <c r="V12" s="13"/>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A13" s="4" t="s">
-        <v>603</v>
+        <v>623</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>645</v>
-      </c>
-      <c r="C13" s="1"/>
+        <v>665</v>
+      </c>
       <c r="D13" s="4">
         <v>10</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>646</v>
-      </c>
-      <c r="F13" s="1"/>
+        <v>666</v>
+      </c>
       <c r="G13" s="4">
         <v>9</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="I13" s="1"/>
+        <v>167</v>
+      </c>
       <c r="J13" s="4">
         <v>9</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>647</v>
-      </c>
-      <c r="L13" s="1"/>
+        <v>667</v>
+      </c>
       <c r="M13" s="10">
         <v>9</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>648</v>
-      </c>
-      <c r="O13" s="1"/>
+        <v>668</v>
+      </c>
       <c r="P13" s="4">
         <v>9</v>
       </c>
       <c r="Q13" s="12" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="R13" s="13"/>
-      <c r="S13" s="1"/>
       <c r="T13" s="4">
         <v>97</v>
       </c>
       <c r="U13" s="12" t="s">
-        <v>649</v>
+        <v>669</v>
       </c>
       <c r="V13" s="13"/>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A14" s="4" t="s">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>650</v>
-      </c>
-      <c r="C14" s="1"/>
+        <v>670</v>
+      </c>
       <c r="D14" s="4" t="s">
-        <v>603</v>
+        <v>623</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="F14" s="1"/>
+        <v>671</v>
+      </c>
       <c r="G14" s="4">
         <v>8</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>652</v>
-      </c>
-      <c r="I14" s="1"/>
+        <v>672</v>
+      </c>
       <c r="J14" s="4" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="L14" s="1"/>
+        <v>673</v>
+      </c>
       <c r="M14" s="10" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>654</v>
-      </c>
-      <c r="O14" s="1"/>
+        <v>674</v>
+      </c>
       <c r="P14" s="4" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="Q14" s="12" t="s">
-        <v>644</v>
+        <v>664</v>
       </c>
       <c r="R14" s="13"/>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="A15" s="4" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>655</v>
-      </c>
-      <c r="C15" s="1"/>
+        <v>675</v>
+      </c>
       <c r="D15" s="4" t="s">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>656</v>
-      </c>
-      <c r="F15" s="1"/>
+        <v>676</v>
+      </c>
       <c r="G15" s="4">
         <v>7</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>657</v>
-      </c>
-      <c r="I15" s="1"/>
+        <v>677</v>
+      </c>
       <c r="J15" s="4" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>658</v>
-      </c>
-      <c r="L15" s="1"/>
+        <v>678</v>
+      </c>
       <c r="M15" s="10" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>659</v>
-      </c>
-      <c r="O15" s="1"/>
+        <v>679</v>
+      </c>
       <c r="P15" s="4" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="Q15" s="12" t="s">
-        <v>649</v>
+        <v>669</v>
       </c>
       <c r="R15" s="13"/>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A16" s="4" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>660</v>
-      </c>
-      <c r="C16" s="1"/>
+        <v>680</v>
+      </c>
       <c r="D16" s="4" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>661</v>
-      </c>
-      <c r="F16" s="1"/>
+        <v>681</v>
+      </c>
       <c r="G16" s="4">
         <v>6</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>662</v>
-      </c>
-      <c r="I16" s="1"/>
+        <v>682</v>
+      </c>
       <c r="J16" s="4" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>663</v>
-      </c>
-      <c r="L16" s="1"/>
+        <v>683</v>
+      </c>
       <c r="M16" s="10" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
       <c r="N16" s="10" t="s">
-        <v>664</v>
+        <v>684</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A17" s="4" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>665</v>
-      </c>
-      <c r="C17" s="1"/>
+        <v>685</v>
+      </c>
       <c r="D17" s="4" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>666</v>
-      </c>
-      <c r="F17" s="1"/>
+        <v>686</v>
+      </c>
       <c r="G17" s="4">
         <v>5</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>667</v>
-      </c>
-      <c r="I17" s="1"/>
+        <v>687</v>
+      </c>
       <c r="J17" s="4" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>668</v>
-      </c>
-      <c r="L17" s="1"/>
+        <v>688</v>
+      </c>
       <c r="M17" s="10" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>669</v>
+        <v>689</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A18" s="4" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>670</v>
-      </c>
-      <c r="C18" s="1"/>
+        <v>690</v>
+      </c>
       <c r="D18" s="4" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>671</v>
-      </c>
-      <c r="F18" s="1"/>
+        <v>691</v>
+      </c>
       <c r="G18" s="4">
         <v>4</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>672</v>
-      </c>
-      <c r="I18" s="1"/>
+        <v>692</v>
+      </c>
       <c r="J18" s="4" t="s">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="L18" s="1"/>
+        <v>693</v>
+      </c>
       <c r="M18" s="10" t="s">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>674</v>
+        <v>694</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -8260,35 +8559,31 @@
         <v>9</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>675</v>
-      </c>
-      <c r="C19" s="1"/>
+        <v>695</v>
+      </c>
       <c r="D19" s="4" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>676</v>
-      </c>
-      <c r="F19" s="1"/>
+        <v>696</v>
+      </c>
       <c r="G19" s="4">
         <v>3</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>677</v>
-      </c>
-      <c r="I19" s="1"/>
+        <v>697</v>
+      </c>
       <c r="J19" s="4" t="s">
-        <v>603</v>
+        <v>623</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>678</v>
-      </c>
-      <c r="L19" s="1"/>
+        <v>698</v>
+      </c>
       <c r="M19" s="10" t="s">
-        <v>603</v>
+        <v>623</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>679</v>
+        <v>699</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -8296,35 +8591,31 @@
         <v>8</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>680</v>
-      </c>
-      <c r="C20" s="1"/>
+        <v>700</v>
+      </c>
       <c r="D20" s="4">
         <v>9</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>681</v>
-      </c>
-      <c r="F20" s="1"/>
+        <v>701</v>
+      </c>
       <c r="G20" s="4">
         <v>2</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>682</v>
-      </c>
-      <c r="I20" s="1"/>
+        <v>702</v>
+      </c>
       <c r="J20" s="4">
         <v>10</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>683</v>
-      </c>
-      <c r="L20" s="1"/>
+        <v>703</v>
+      </c>
       <c r="M20" s="10">
         <v>10</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>684</v>
+        <v>704</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -8332,35 +8623,31 @@
         <v>7</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>685</v>
-      </c>
-      <c r="C21" s="1"/>
+        <v>705</v>
+      </c>
       <c r="D21" s="4">
         <v>8</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>686</v>
-      </c>
-      <c r="F21" s="1"/>
+        <v>706</v>
+      </c>
       <c r="G21" s="4">
         <v>1</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>687</v>
-      </c>
-      <c r="I21" s="1"/>
+        <v>707</v>
+      </c>
       <c r="J21" s="4">
         <v>11</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>688</v>
-      </c>
-      <c r="L21" s="1"/>
+        <v>708</v>
+      </c>
       <c r="M21" s="10">
         <v>11</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>689</v>
+        <v>709</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -8368,35 +8655,31 @@
         <v>6</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>690</v>
-      </c>
-      <c r="C22" s="1"/>
+        <v>710</v>
+      </c>
       <c r="D22" s="4">
         <v>7</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>691</v>
-      </c>
-      <c r="F22" s="1"/>
+        <v>711</v>
+      </c>
       <c r="G22" s="4">
         <v>0</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>692</v>
-      </c>
-      <c r="I22" s="1"/>
+        <v>712</v>
+      </c>
       <c r="J22" s="4">
         <v>12</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>693</v>
-      </c>
-      <c r="L22" s="1"/>
+        <v>713</v>
+      </c>
       <c r="M22" s="10">
         <v>12</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>694</v>
+        <v>714</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -8404,31 +8687,25 @@
         <v>5</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>695</v>
-      </c>
-      <c r="C23" s="1"/>
+        <v>715</v>
+      </c>
       <c r="D23" s="4">
         <v>6</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
+        <v>716</v>
+      </c>
       <c r="J23" s="4">
         <v>13</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>697</v>
-      </c>
-      <c r="L23" s="1"/>
+        <v>717</v>
+      </c>
       <c r="M23" s="10">
         <v>13</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>698</v>
+        <v>718</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -8436,31 +8713,25 @@
         <v>4</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>699</v>
-      </c>
-      <c r="C24" s="1"/>
+        <v>719</v>
+      </c>
       <c r="D24" s="4">
         <v>5</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>700</v>
-      </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
+        <v>720</v>
+      </c>
       <c r="J24" s="4">
         <v>14</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>701</v>
-      </c>
-      <c r="L24" s="1"/>
+        <v>721</v>
+      </c>
       <c r="M24" s="10">
         <v>14</v>
       </c>
       <c r="N24" s="10" t="s">
-        <v>702</v>
+        <v>722</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="4:14">
@@ -8468,24 +8739,19 @@
         <v>4</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
+        <v>173</v>
+      </c>
       <c r="J25" s="4">
         <v>15</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>703</v>
-      </c>
-      <c r="L25" s="1"/>
+        <v>723</v>
+      </c>
       <c r="M25" s="10">
         <v>15</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>704</v>
+        <v>724</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="4:14">
@@ -8493,24 +8759,19 @@
         <v>3</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>705</v>
-      </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
+        <v>725</v>
+      </c>
       <c r="J26" s="4">
         <v>16</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>706</v>
-      </c>
-      <c r="L26" s="1"/>
+        <v>726</v>
+      </c>
       <c r="M26" s="10">
         <v>16</v>
       </c>
       <c r="N26" s="10" t="s">
-        <v>707</v>
+        <v>727</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="4:14">
@@ -8518,24 +8779,19 @@
         <v>2</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
+        <v>728</v>
+      </c>
       <c r="J27" s="4">
         <v>17</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>709</v>
-      </c>
-      <c r="L27" s="1"/>
+        <v>729</v>
+      </c>
       <c r="M27" s="10">
         <v>17</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>710</v>
+        <v>730</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="4:14">
@@ -8543,24 +8799,19 @@
         <v>1</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
+        <v>167</v>
+      </c>
       <c r="J28" s="4">
         <v>18</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>711</v>
-      </c>
-      <c r="L28" s="1"/>
+        <v>731</v>
+      </c>
       <c r="M28" s="10">
         <v>18</v>
       </c>
       <c r="N28" s="10" t="s">
-        <v>712</v>
+        <v>732</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="10:14">
@@ -8568,72 +8819,70 @@
         <v>19</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>713</v>
-      </c>
-      <c r="L29" s="1"/>
+        <v>733</v>
+      </c>
       <c r="M29" s="10">
         <v>19</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>714</v>
+        <v>734</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="10:14">
       <c r="J30" s="4" t="s">
-        <v>715</v>
+        <v>735</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>716</v>
-      </c>
-      <c r="L30" s="1"/>
+        <v>736</v>
+      </c>
       <c r="M30" s="10" t="s">
-        <v>715</v>
+        <v>735</v>
       </c>
       <c r="N30" s="10" t="s">
-        <v>717</v>
+        <v>737</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A31" s="7" t="s">
-        <v>718</v>
+        <v>738</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>719</v>
+        <v>739</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="10:11">
       <c r="J32" s="4" t="s">
-        <v>721</v>
+        <v>741</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>722</v>
+        <v>742</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="10:11">
       <c r="J33" s="4" t="s">
-        <v>723</v>
+        <v>743</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>724</v>
+        <v>744</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="10:11">
       <c r="J34" s="4" t="s">
-        <v>725</v>
+        <v>745</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>726</v>
+        <v>746</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="10:11">
       <c r="J35" s="4" t="s">
-        <v>727</v>
+        <v>747</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>728</v>
+        <v>748</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="10:11">
@@ -8641,7 +8890,15 @@
         <v>20</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>729</v>
+        <v>749</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="10:11">
+      <c r="J37" s="4">
+        <v>21</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>750</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:17">
@@ -8649,667 +8906,638 @@
         <v>32</v>
       </c>
       <c r="B43" s="3"/>
-      <c r="C43" s="1"/>
       <c r="D43" s="8" t="s">
-        <v>730</v>
+        <v>751</v>
       </c>
       <c r="E43" s="8"/>
       <c r="G43" s="2" t="s">
         <v>51</v>
       </c>
       <c r="H43" s="3"/>
-      <c r="I43" s="1"/>
       <c r="J43" s="2" t="s">
-        <v>731</v>
+        <v>752</v>
       </c>
       <c r="K43" s="11"/>
       <c r="L43" s="11"/>
       <c r="M43" s="11"/>
       <c r="N43" s="11"/>
       <c r="P43" s="8" t="s">
-        <v>732</v>
+        <v>753</v>
       </c>
       <c r="Q43" s="8"/>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A44" s="4" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>733</v>
-      </c>
-      <c r="C44" s="1"/>
+        <v>754</v>
+      </c>
       <c r="D44" s="9" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>733</v>
+        <v>754</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>734</v>
-      </c>
-      <c r="I44" s="1"/>
+        <v>755</v>
+      </c>
       <c r="J44" s="4" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="K44" s="12" t="s">
-        <v>736</v>
+        <v>757</v>
       </c>
       <c r="L44" s="11"/>
       <c r="M44" s="11"/>
       <c r="N44" s="13"/>
       <c r="P44" s="9" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="Q44" s="9" t="s">
-        <v>734</v>
+        <v>755</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A45" s="4" t="s">
-        <v>737</v>
+        <v>758</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>738</v>
-      </c>
-      <c r="C45" s="1"/>
+        <v>759</v>
+      </c>
       <c r="D45" s="9" t="s">
-        <v>739</v>
+        <v>760</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>738</v>
+        <v>759</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>740</v>
+        <v>761</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>741</v>
-      </c>
-      <c r="I45" s="1"/>
+        <v>762</v>
+      </c>
       <c r="J45" s="4" t="s">
-        <v>742</v>
+        <v>763</v>
       </c>
       <c r="K45" s="12" t="s">
-        <v>743</v>
+        <v>764</v>
       </c>
       <c r="L45" s="11"/>
       <c r="M45" s="11"/>
       <c r="N45" s="13"/>
       <c r="P45" s="9" t="s">
-        <v>740</v>
+        <v>761</v>
       </c>
       <c r="Q45" s="9" t="s">
-        <v>744</v>
+        <v>765</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A46" s="4" t="s">
-        <v>745</v>
+        <v>766</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="C46" s="1"/>
+        <v>767</v>
+      </c>
       <c r="D46" s="9" t="s">
-        <v>747</v>
+        <v>768</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>746</v>
+        <v>767</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>748</v>
+        <v>769</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>749</v>
+        <v>770</v>
       </c>
       <c r="P46" s="9" t="s">
-        <v>748</v>
+        <v>769</v>
       </c>
       <c r="Q46" s="9" t="s">
-        <v>750</v>
+        <v>771</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A47" s="4" t="s">
-        <v>751</v>
+        <v>772</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>752</v>
-      </c>
-      <c r="C47" s="1"/>
+        <v>773</v>
+      </c>
       <c r="D47" s="9" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>752</v>
+        <v>773</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>754</v>
+        <v>775</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>755</v>
+        <v>776</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>754</v>
+        <v>775</v>
       </c>
       <c r="Q47" s="9" t="s">
-        <v>756</v>
+        <v>777</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A48" s="4" t="s">
-        <v>757</v>
+        <v>778</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>758</v>
-      </c>
-      <c r="C48" s="1"/>
+        <v>779</v>
+      </c>
       <c r="D48" s="9" t="s">
-        <v>759</v>
+        <v>780</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>758</v>
+        <v>779</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>760</v>
+        <v>781</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>761</v>
+        <v>782</v>
       </c>
       <c r="P48" s="9" t="s">
-        <v>760</v>
+        <v>781</v>
       </c>
       <c r="Q48" s="9" t="s">
-        <v>762</v>
+        <v>783</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A49" s="4" t="s">
-        <v>763</v>
+        <v>784</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>764</v>
-      </c>
-      <c r="C49" s="1"/>
+        <v>785</v>
+      </c>
       <c r="D49" s="9" t="s">
-        <v>765</v>
+        <v>786</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>764</v>
+        <v>785</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>766</v>
+        <v>787</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>767</v>
+        <v>788</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>766</v>
+        <v>787</v>
       </c>
       <c r="Q49" s="9" t="s">
-        <v>768</v>
+        <v>789</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A50" s="4" t="s">
-        <v>769</v>
+        <v>790</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>770</v>
-      </c>
-      <c r="C50" s="1"/>
+        <v>791</v>
+      </c>
       <c r="D50" s="9" t="s">
-        <v>771</v>
+        <v>792</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>770</v>
+        <v>791</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>772</v>
+        <v>793</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>773</v>
+        <v>794</v>
       </c>
       <c r="P50" s="9" t="s">
-        <v>772</v>
+        <v>793</v>
       </c>
       <c r="Q50" s="9" t="s">
-        <v>774</v>
+        <v>795</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A51" s="4" t="s">
-        <v>775</v>
+        <v>796</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>776</v>
-      </c>
-      <c r="C51" s="1"/>
+        <v>797</v>
+      </c>
       <c r="D51" s="9" t="s">
-        <v>777</v>
+        <v>798</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>776</v>
+        <v>797</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>778</v>
+        <v>799</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>779</v>
+        <v>800</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>778</v>
+        <v>799</v>
       </c>
       <c r="Q51" s="9" t="s">
-        <v>780</v>
+        <v>801</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A52" s="4" t="s">
-        <v>781</v>
+        <v>802</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>782</v>
-      </c>
-      <c r="C52" s="1"/>
+        <v>803</v>
+      </c>
       <c r="D52" s="9" t="s">
-        <v>783</v>
+        <v>804</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>782</v>
+        <v>803</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>784</v>
+        <v>805</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>785</v>
+        <v>806</v>
       </c>
       <c r="P52" s="9" t="s">
-        <v>784</v>
+        <v>805</v>
       </c>
       <c r="Q52" s="9" t="s">
-        <v>786</v>
+        <v>807</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A53" s="4" t="s">
-        <v>787</v>
+        <v>808</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>788</v>
-      </c>
-      <c r="C53" s="1"/>
+        <v>809</v>
+      </c>
       <c r="D53" s="9" t="s">
-        <v>789</v>
+        <v>810</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>790</v>
+        <v>811</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>791</v>
+        <v>812</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>790</v>
+        <v>811</v>
       </c>
       <c r="Q53" s="9" t="s">
-        <v>792</v>
+        <v>813</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A54" s="4" t="s">
-        <v>793</v>
+        <v>814</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>794</v>
-      </c>
-      <c r="C54" s="1"/>
+        <v>815</v>
+      </c>
       <c r="D54" s="9" t="s">
-        <v>795</v>
+        <v>816</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>794</v>
+        <v>815</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>796</v>
+        <v>817</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>797</v>
+        <v>818</v>
       </c>
       <c r="P54" s="9" t="s">
-        <v>796</v>
+        <v>817</v>
       </c>
       <c r="Q54" s="9" t="s">
-        <v>798</v>
+        <v>819</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A55" s="4" t="s">
-        <v>799</v>
+        <v>820</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>800</v>
-      </c>
-      <c r="C55" s="1"/>
+        <v>821</v>
+      </c>
       <c r="D55" s="9" t="s">
-        <v>801</v>
+        <v>822</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>800</v>
+        <v>821</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>802</v>
+        <v>823</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>803</v>
+        <v>824</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>802</v>
+        <v>823</v>
       </c>
       <c r="Q55" s="9" t="s">
-        <v>804</v>
+        <v>825</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A56" s="4" t="s">
-        <v>805</v>
+        <v>826</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>806</v>
-      </c>
-      <c r="C56" s="1"/>
+        <v>827</v>
+      </c>
       <c r="D56" s="9" t="s">
-        <v>807</v>
+        <v>828</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>806</v>
+        <v>827</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="H56" s="4">
         <v>0.47</v>
       </c>
       <c r="P56" s="9" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="Q56" s="9" t="s">
-        <v>809</v>
+        <v>830</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A57" s="4" t="s">
-        <v>810</v>
+        <v>831</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>811</v>
-      </c>
-      <c r="C57" s="1"/>
+        <v>832</v>
+      </c>
       <c r="D57" s="9" t="s">
-        <v>812</v>
+        <v>833</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>811</v>
+        <v>832</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>813</v>
+        <v>834</v>
       </c>
       <c r="H57" s="4">
         <v>0.35</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>813</v>
+        <v>834</v>
       </c>
       <c r="Q57" s="9" t="s">
-        <v>814</v>
+        <v>835</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="1:17">
       <c r="A58" s="4" t="s">
-        <v>815</v>
+        <v>836</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>816</v>
-      </c>
-      <c r="C58" s="1"/>
+        <v>837</v>
+      </c>
       <c r="D58" s="9" t="s">
-        <v>817</v>
+        <v>838</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>816</v>
+        <v>837</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>818</v>
+        <v>839</v>
       </c>
       <c r="H58" s="4">
         <v>0.26</v>
       </c>
       <c r="P58" s="9" t="s">
-        <v>818</v>
+        <v>839</v>
       </c>
       <c r="Q58" s="9" t="s">
-        <v>819</v>
+        <v>840</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A59" s="4" t="s">
-        <v>820</v>
+        <v>841</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="C59" s="1"/>
+        <v>842</v>
+      </c>
       <c r="D59" s="9" t="s">
-        <v>822</v>
+        <v>843</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>821</v>
+        <v>842</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>823</v>
+        <v>844</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>824</v>
+        <v>845</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A60" s="4" t="s">
-        <v>825</v>
+        <v>846</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>826</v>
+        <v>847</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>827</v>
+        <v>848</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>826</v>
+        <v>847</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A61" s="4" t="s">
-        <v>828</v>
+        <v>849</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>829</v>
+        <v>850</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>830</v>
+        <v>851</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>829</v>
+        <v>850</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A62" s="4" t="s">
-        <v>760</v>
+        <v>781</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>831</v>
+        <v>852</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>832</v>
+        <v>853</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>831</v>
+        <v>852</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A63" s="4" t="s">
-        <v>772</v>
+        <v>793</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>833</v>
+        <v>854</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>834</v>
+        <v>855</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>835</v>
+        <v>856</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="4:5">
       <c r="D64" s="9" t="s">
-        <v>836</v>
+        <v>857</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>837</v>
+        <v>858</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="4:5">
       <c r="D65" s="9" t="s">
-        <v>838</v>
+        <v>859</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>839</v>
+        <v>860</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="4:5">
       <c r="D66" s="9" t="s">
-        <v>840</v>
+        <v>861</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>841</v>
+        <v>862</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" customHeight="1" spans="4:5">
       <c r="D67" s="9" t="s">
-        <v>842</v>
+        <v>863</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>843</v>
+        <v>864</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" customHeight="1" spans="4:5">
       <c r="D68" s="9" t="s">
-        <v>760</v>
+        <v>781</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>844</v>
+        <v>865</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1" spans="4:5">
       <c r="D69" s="9" t="s">
-        <v>772</v>
+        <v>793</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>845</v>
+        <v>866</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A77" s="2" t="s">
-        <v>846</v>
+        <v>867</v>
       </c>
       <c r="B77" s="11"/>
       <c r="C77" s="11"/>
-      <c r="D77" s="1"/>
       <c r="E77" s="2" t="s">
-        <v>847</v>
+        <v>868</v>
       </c>
       <c r="F77" s="11"/>
       <c r="G77" s="11"/>
-      <c r="H77" s="1"/>
       <c r="I77" s="2" t="s">
-        <v>848</v>
+        <v>869</v>
       </c>
       <c r="J77" s="11"/>
       <c r="K77" s="11"/>
-      <c r="L77" s="1"/>
       <c r="M77" s="2" t="s">
-        <v>849</v>
+        <v>870</v>
       </c>
       <c r="N77" s="11"/>
       <c r="O77" s="11"/>
     </row>
     <row r="78" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A78" s="4" t="s">
-        <v>850</v>
+        <v>871</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="C78" s="14"/>
-      <c r="D78" s="1"/>
       <c r="E78" s="4" t="s">
-        <v>850</v>
+        <v>871</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="G78" s="14"/>
-      <c r="H78" s="1"/>
       <c r="I78" s="4" t="s">
-        <v>850</v>
+        <v>871</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="K78" s="14"/>
-      <c r="L78" s="1"/>
       <c r="M78" s="4" t="s">
-        <v>850</v>
+        <v>871</v>
       </c>
       <c r="N78" s="4" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="O78" s="14"/>
     </row>
     <row r="79" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A79" s="14"/>
       <c r="B79" s="4" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>742</v>
-      </c>
-      <c r="D79" s="1"/>
+        <v>763</v>
+      </c>
       <c r="E79" s="14"/>
       <c r="F79" s="4" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>742</v>
-      </c>
-      <c r="H79" s="1"/>
+        <v>763</v>
+      </c>
       <c r="I79" s="14"/>
       <c r="J79" s="4" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>742</v>
-      </c>
-      <c r="L79" s="1"/>
+        <v>763</v>
+      </c>
       <c r="M79" s="14"/>
       <c r="N79" s="4" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>742</v>
+        <v>763</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -9322,7 +9550,6 @@
       <c r="C80" s="4">
         <v>0.1</v>
       </c>
-      <c r="D80" s="1"/>
       <c r="E80" s="4">
         <v>1</v>
       </c>
@@ -9332,7 +9559,6 @@
       <c r="G80" s="4">
         <v>0.9</v>
       </c>
-      <c r="H80" s="1"/>
       <c r="I80" s="4">
         <v>1</v>
       </c>
@@ -9342,7 +9568,6 @@
       <c r="K80" s="4">
         <v>1.1</v>
       </c>
-      <c r="L80" s="1"/>
       <c r="M80" s="4">
         <v>1</v>
       </c>
@@ -9363,7 +9588,6 @@
       <c r="C81" s="4">
         <v>0.2</v>
       </c>
-      <c r="D81" s="1"/>
       <c r="E81" s="4">
         <v>2</v>
       </c>
@@ -9373,7 +9597,6 @@
       <c r="G81" s="4">
         <v>1.1</v>
       </c>
-      <c r="H81" s="1"/>
       <c r="I81" s="4">
         <v>2</v>
       </c>
@@ -9383,7 +9606,6 @@
       <c r="K81" s="4">
         <v>1.3</v>
       </c>
-      <c r="L81" s="1"/>
       <c r="M81" s="4">
         <v>2</v>
       </c>
@@ -9404,7 +9626,6 @@
       <c r="C82" s="4">
         <v>0.5</v>
       </c>
-      <c r="D82" s="1"/>
       <c r="E82" s="4">
         <v>3</v>
       </c>
@@ -9414,7 +9635,6 @@
       <c r="G82" s="4">
         <v>1.3</v>
       </c>
-      <c r="H82" s="1"/>
       <c r="I82" s="4">
         <v>3</v>
       </c>
@@ -9424,7 +9644,6 @@
       <c r="K82" s="4">
         <v>1.5</v>
       </c>
-      <c r="L82" s="1"/>
       <c r="M82" s="4">
         <v>3</v>
       </c>
@@ -9445,7 +9664,6 @@
       <c r="C83" s="4">
         <v>0.7</v>
       </c>
-      <c r="D83" s="1"/>
       <c r="E83" s="4">
         <v>4</v>
       </c>
@@ -9455,7 +9673,6 @@
       <c r="G83" s="4">
         <v>1.5</v>
       </c>
-      <c r="H83" s="1"/>
       <c r="I83" s="4">
         <v>4</v>
       </c>
@@ -9465,7 +9682,6 @@
       <c r="K83" s="4">
         <v>1.9</v>
       </c>
-      <c r="L83" s="1"/>
       <c r="M83" s="4">
         <v>4</v>
       </c>
@@ -9486,7 +9702,6 @@
       <c r="C84" s="4">
         <v>0.9</v>
       </c>
-      <c r="D84" s="1"/>
       <c r="E84" s="4">
         <v>5</v>
       </c>
@@ -9496,7 +9711,6 @@
       <c r="G84" s="4">
         <v>1.9</v>
       </c>
-      <c r="H84" s="1"/>
       <c r="I84" s="4">
         <v>5</v>
       </c>
@@ -9506,7 +9720,6 @@
       <c r="K84" s="4">
         <v>2.69</v>
       </c>
-      <c r="L84" s="1"/>
       <c r="M84" s="4">
         <v>5</v>
       </c>
@@ -9527,7 +9740,6 @@
       <c r="C85" s="4">
         <v>1.1</v>
       </c>
-      <c r="D85" s="1"/>
       <c r="E85" s="4">
         <v>6</v>
       </c>
@@ -9537,7 +9749,6 @@
       <c r="G85" s="4">
         <v>2.3</v>
       </c>
-      <c r="H85" s="1"/>
       <c r="I85" s="4">
         <v>6</v>
       </c>
@@ -9547,7 +9758,6 @@
       <c r="K85" s="4">
         <v>3.56</v>
       </c>
-      <c r="L85" s="1"/>
       <c r="M85" s="4">
         <v>6</v>
       </c>
@@ -9568,7 +9778,6 @@
       <c r="C86" s="4">
         <v>1.3</v>
       </c>
-      <c r="D86" s="1"/>
       <c r="E86" s="4">
         <v>7</v>
       </c>
@@ -9578,7 +9787,6 @@
       <c r="G86" s="4">
         <v>3.15</v>
       </c>
-      <c r="H86" s="1"/>
       <c r="I86" s="4">
         <v>7</v>
       </c>
@@ -9588,7 +9796,6 @@
       <c r="K86" s="4">
         <v>5.36</v>
       </c>
-      <c r="L86" s="1"/>
       <c r="M86" s="4">
         <v>7</v>
       </c>
@@ -9609,7 +9816,6 @@
       <c r="C87" s="4">
         <v>1.5</v>
       </c>
-      <c r="D87" s="1"/>
       <c r="E87" s="4">
         <v>8</v>
       </c>
@@ -9619,7 +9825,6 @@
       <c r="G87" s="4">
         <v>4.14</v>
       </c>
-      <c r="H87" s="1"/>
       <c r="I87" s="4">
         <v>8</v>
       </c>
@@ -9629,7 +9834,6 @@
       <c r="K87" s="4">
         <v>7.32</v>
       </c>
-      <c r="L87" s="1"/>
       <c r="M87" s="4">
         <v>8</v>
       </c>
@@ -9650,7 +9854,6 @@
       <c r="C88" s="4">
         <v>1.9</v>
       </c>
-      <c r="D88" s="1"/>
       <c r="E88" s="4">
         <v>9</v>
       </c>
@@ -9660,7 +9863,6 @@
       <c r="G88" s="4">
         <v>5.36</v>
       </c>
-      <c r="H88" s="1"/>
       <c r="I88" s="4">
         <v>9</v>
       </c>
@@ -9670,7 +9872,6 @@
       <c r="K88" s="4">
         <v>9.81</v>
       </c>
-      <c r="L88" s="1"/>
       <c r="M88" s="4">
         <v>9</v>
       </c>
@@ -9683,7 +9884,7 @@
     </row>
     <row r="89" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A89" s="4" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="B89" s="4">
         <v>2.3</v>
@@ -9691,9 +9892,8 @@
       <c r="C89" s="4">
         <v>2.3</v>
       </c>
-      <c r="D89" s="1"/>
       <c r="E89" s="4" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="F89" s="4">
         <v>6.89</v>
@@ -9701,9 +9901,8 @@
       <c r="G89" s="4">
         <v>6.89</v>
       </c>
-      <c r="H89" s="1"/>
       <c r="I89" s="4" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="J89" s="4">
         <v>13.22</v>
@@ -9711,9 +9910,8 @@
       <c r="K89" s="4">
         <v>13.22</v>
       </c>
-      <c r="L89" s="1"/>
       <c r="M89" s="4" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="N89" s="4">
         <v>3.15</v>
@@ -9724,7 +9922,7 @@
     </row>
     <row r="90" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A90" s="4" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="B90" s="4">
         <v>2.7</v>
@@ -9732,9 +9930,8 @@
       <c r="C90" s="4">
         <v>2.7</v>
       </c>
-      <c r="D90" s="1"/>
       <c r="E90" s="4" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="F90" s="4">
         <v>7.88</v>
@@ -9742,9 +9939,8 @@
       <c r="G90" s="4">
         <v>7.88</v>
       </c>
-      <c r="H90" s="1"/>
       <c r="I90" s="4" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="J90" s="4">
         <v>17.38</v>
@@ -9752,9 +9948,8 @@
       <c r="K90" s="4">
         <v>17.38</v>
       </c>
-      <c r="L90" s="1"/>
       <c r="M90" s="4" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="N90" s="4">
         <v>4.14</v>
@@ -9765,7 +9960,7 @@
     </row>
     <row r="91" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A91" s="4" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
       <c r="B91" s="4">
         <v>3.2</v>
@@ -9773,9 +9968,8 @@
       <c r="C91" s="4">
         <v>3.2</v>
       </c>
-      <c r="D91" s="1"/>
       <c r="E91" s="4" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
       <c r="F91" s="4">
         <v>10.9</v>
@@ -9783,9 +9977,8 @@
       <c r="G91" s="4">
         <v>10.9</v>
       </c>
-      <c r="H91" s="1"/>
       <c r="I91" s="4" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
       <c r="J91" s="4">
         <v>20.54</v>
@@ -9793,9 +9986,8 @@
       <c r="K91" s="4">
         <v>20.54</v>
       </c>
-      <c r="L91" s="1"/>
       <c r="M91" s="4" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
       <c r="N91" s="4">
         <v>5.36</v>
@@ -9806,7 +9998,7 @@
     </row>
     <row r="92" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A92" s="4" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="B92" s="4">
         <v>3.5</v>
@@ -9814,9 +10006,8 @@
       <c r="C92" s="4">
         <v>3.5</v>
       </c>
-      <c r="D92" s="1"/>
       <c r="E92" s="4" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="F92" s="4">
         <v>13.22</v>
@@ -9824,9 +10015,8 @@
       <c r="G92" s="4">
         <v>13.22</v>
       </c>
-      <c r="H92" s="1"/>
       <c r="I92" s="4" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="J92" s="4">
         <v>23.9</v>
@@ -9834,9 +10024,8 @@
       <c r="K92" s="4">
         <v>23.9</v>
       </c>
-      <c r="L92" s="1"/>
       <c r="M92" s="4" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="N92" s="4">
         <v>6.45</v>
@@ -9847,7 +10036,7 @@
     </row>
     <row r="93" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A93" s="4" t="s">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="B93" s="4">
         <v>4.1</v>
@@ -9855,9 +10044,8 @@
       <c r="C93" s="4">
         <v>4.1</v>
       </c>
-      <c r="D93" s="1"/>
       <c r="E93" s="4" t="s">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="F93" s="4">
         <v>17.38</v>
@@ -9865,9 +10053,8 @@
       <c r="G93" s="4">
         <v>17.38</v>
       </c>
-      <c r="H93" s="1"/>
       <c r="I93" s="4" t="s">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="J93" s="4">
         <v>27.5</v>
@@ -9875,9 +10062,8 @@
       <c r="K93" s="4">
         <v>27.5</v>
       </c>
-      <c r="L93" s="1"/>
       <c r="M93" s="4" t="s">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="N93" s="4">
         <v>7.88</v>
@@ -9888,7 +10074,7 @@
     </row>
     <row r="94" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A94" s="4" t="s">
-        <v>603</v>
+        <v>623</v>
       </c>
       <c r="B94" s="4">
         <v>4.7</v>
@@ -9896,9 +10082,8 @@
       <c r="C94" s="4">
         <v>4.7</v>
       </c>
-      <c r="D94" s="1"/>
       <c r="E94" s="4" t="s">
-        <v>603</v>
+        <v>623</v>
       </c>
       <c r="F94" s="4">
         <v>20.54</v>
@@ -9906,9 +10091,8 @@
       <c r="G94" s="4">
         <v>20.54</v>
       </c>
-      <c r="H94" s="1"/>
       <c r="I94" s="4" t="s">
-        <v>603</v>
+        <v>623</v>
       </c>
       <c r="J94" s="4">
         <v>34.74</v>
@@ -9916,9 +10100,8 @@
       <c r="K94" s="4">
         <v>34.74</v>
       </c>
-      <c r="L94" s="1"/>
       <c r="M94" s="4" t="s">
-        <v>603</v>
+        <v>623</v>
       </c>
       <c r="N94" s="4">
         <v>9.81</v>
@@ -9937,7 +10120,6 @@
       <c r="C95" s="4">
         <v>5.3</v>
       </c>
-      <c r="D95" s="1"/>
       <c r="E95" s="4">
         <v>10</v>
       </c>
@@ -9947,7 +10129,6 @@
       <c r="G95" s="4">
         <v>23.95</v>
       </c>
-      <c r="H95" s="1"/>
       <c r="I95" s="4">
         <v>10</v>
       </c>
@@ -9957,7 +10138,6 @@
       <c r="K95" s="4">
         <v>41.07</v>
       </c>
-      <c r="L95" s="1"/>
       <c r="M95" s="4">
         <v>10</v>
       </c>
@@ -9978,7 +10158,6 @@
       <c r="C96" s="4">
         <v>5.9</v>
       </c>
-      <c r="D96" s="1"/>
       <c r="E96" s="4">
         <v>11</v>
       </c>
@@ -9988,7 +10167,6 @@
       <c r="G96" s="4">
         <v>27.59</v>
       </c>
-      <c r="H96" s="1"/>
       <c r="I96" s="4">
         <v>11</v>
       </c>
@@ -9998,7 +10176,6 @@
       <c r="K96" s="4">
         <v>43.6</v>
       </c>
-      <c r="L96" s="1"/>
       <c r="M96" s="4">
         <v>11</v>
       </c>
@@ -10019,7 +10196,6 @@
       <c r="C97" s="4">
         <v>6.5</v>
       </c>
-      <c r="D97" s="1"/>
       <c r="E97" s="4">
         <v>12</v>
       </c>
@@ -10029,7 +10205,6 @@
       <c r="G97" s="4">
         <v>31.27</v>
       </c>
-      <c r="H97" s="1"/>
       <c r="I97" s="4">
         <v>12</v>
       </c>
@@ -10039,7 +10214,6 @@
       <c r="K97" s="4">
         <v>46.5</v>
       </c>
-      <c r="L97" s="1"/>
       <c r="M97" s="4">
         <v>12</v>
       </c>
@@ -10060,7 +10234,6 @@
       <c r="C98" s="4">
         <v>7.3</v>
       </c>
-      <c r="D98" s="1"/>
       <c r="E98" s="4">
         <v>13</v>
       </c>
@@ -10070,7 +10243,6 @@
       <c r="G98" s="4">
         <v>38.54</v>
       </c>
-      <c r="H98" s="1"/>
       <c r="I98" s="4">
         <v>13</v>
       </c>
@@ -10080,7 +10252,6 @@
       <c r="K98" s="4">
         <v>50.2</v>
       </c>
-      <c r="L98" s="1"/>
       <c r="M98" s="4">
         <v>13</v>
       </c>
@@ -10101,7 +10272,6 @@
       <c r="C99" s="4">
         <v>8.9</v>
       </c>
-      <c r="D99" s="1"/>
       <c r="E99" s="4">
         <v>14</v>
       </c>
@@ -10111,7 +10281,6 @@
       <c r="G99" s="4">
         <v>43.6</v>
       </c>
-      <c r="H99" s="1"/>
       <c r="I99" s="4">
         <v>14</v>
       </c>
@@ -10121,7 +10290,6 @@
       <c r="K99" s="4">
         <v>54.6</v>
       </c>
-      <c r="L99" s="1"/>
       <c r="M99" s="4">
         <v>14</v>
       </c>
@@ -10142,7 +10310,6 @@
       <c r="C100" s="4">
         <v>9.8</v>
       </c>
-      <c r="D100" s="1"/>
       <c r="E100" s="4">
         <v>15</v>
       </c>
@@ -10152,7 +10319,6 @@
       <c r="G100" s="4">
         <v>46.5</v>
       </c>
-      <c r="H100" s="1"/>
       <c r="I100" s="4">
         <v>15</v>
       </c>
@@ -10162,7 +10328,6 @@
       <c r="K100" s="4">
         <v>57.3</v>
       </c>
-      <c r="L100" s="1"/>
       <c r="M100" s="4">
         <v>15</v>
       </c>
@@ -10183,7 +10348,6 @@
       <c r="C101" s="4">
         <v>11.91</v>
       </c>
-      <c r="D101" s="1"/>
       <c r="E101" s="4">
         <v>16</v>
       </c>
@@ -10193,7 +10357,6 @@
       <c r="G101" s="4">
         <v>50.2</v>
       </c>
-      <c r="H101" s="1"/>
       <c r="I101" s="4">
         <v>16</v>
       </c>
@@ -10203,7 +10366,6 @@
       <c r="K101" s="4">
         <v>63</v>
       </c>
-      <c r="L101" s="1"/>
       <c r="M101" s="4">
         <v>16</v>
       </c>
@@ -10224,7 +10386,6 @@
       <c r="C102" s="4">
         <v>14.66</v>
       </c>
-      <c r="D102" s="1"/>
       <c r="E102" s="4">
         <v>17</v>
       </c>
@@ -10234,7 +10395,6 @@
       <c r="G102" s="4">
         <v>54.2</v>
       </c>
-      <c r="H102" s="1"/>
       <c r="I102" s="4">
         <v>17</v>
       </c>
@@ -10244,7 +10404,6 @@
       <c r="K102" s="4">
         <v>69.1</v>
       </c>
-      <c r="L102" s="1"/>
       <c r="M102" s="4">
         <v>17</v>
       </c>
@@ -10265,7 +10424,6 @@
       <c r="C103" s="4">
         <v>17.38</v>
       </c>
-      <c r="D103" s="1"/>
       <c r="E103" s="4">
         <v>18</v>
       </c>
@@ -10275,7 +10433,6 @@
       <c r="G103" s="4">
         <v>57.3</v>
       </c>
-      <c r="H103" s="1"/>
       <c r="I103" s="4">
         <v>18</v>
       </c>
@@ -10285,7 +10442,6 @@
       <c r="K103" s="4">
         <v>75.2</v>
       </c>
-      <c r="L103" s="1"/>
       <c r="M103" s="4">
         <v>18</v>
       </c>
@@ -10306,7 +10462,6 @@
       <c r="C104" s="4">
         <v>20.54</v>
       </c>
-      <c r="D104" s="1"/>
       <c r="E104" s="4">
         <v>19</v>
       </c>
@@ -10316,7 +10471,6 @@
       <c r="G104" s="4">
         <v>60.1</v>
       </c>
-      <c r="H104" s="1"/>
       <c r="I104" s="4">
         <v>19</v>
       </c>
@@ -10326,7 +10480,6 @@
       <c r="K104" s="4">
         <v>80.5</v>
       </c>
-      <c r="L104" s="1"/>
       <c r="M104" s="4">
         <v>19</v>
       </c>
@@ -10339,7 +10492,7 @@
     </row>
     <row r="105" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A105" s="4" t="s">
-        <v>715</v>
+        <v>735</v>
       </c>
       <c r="B105" s="4">
         <v>27.59</v>
@@ -10347,9 +10500,8 @@
       <c r="C105" s="4">
         <v>27.59</v>
       </c>
-      <c r="D105" s="1"/>
       <c r="E105" s="4" t="s">
-        <v>715</v>
+        <v>735</v>
       </c>
       <c r="F105" s="4">
         <v>63.2</v>
@@ -10357,9 +10509,8 @@
       <c r="G105" s="4">
         <v>63.2</v>
       </c>
-      <c r="H105" s="1"/>
       <c r="I105" s="4" t="s">
-        <v>715</v>
+        <v>735</v>
       </c>
       <c r="J105" s="4">
         <v>90</v>
@@ -10367,9 +10518,8 @@
       <c r="K105" s="4">
         <v>90</v>
       </c>
-      <c r="L105" s="1"/>
       <c r="M105" s="4" t="s">
-        <v>715</v>
+        <v>735</v>
       </c>
       <c r="N105" s="4">
         <v>43.62</v>
@@ -10380,7 +10530,7 @@
     </row>
     <row r="106" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A106" s="4" t="s">
-        <v>719</v>
+        <v>739</v>
       </c>
       <c r="B106" s="4">
         <v>34.74</v>
@@ -10388,9 +10538,8 @@
       <c r="C106" s="4">
         <v>34.74</v>
       </c>
-      <c r="D106" s="1"/>
       <c r="E106" s="4" t="s">
-        <v>719</v>
+        <v>739</v>
       </c>
       <c r="F106" s="4">
         <v>66</v>
@@ -10398,9 +10547,8 @@
       <c r="G106" s="4">
         <v>66</v>
       </c>
-      <c r="H106" s="1"/>
       <c r="I106" s="4" t="s">
-        <v>719</v>
+        <v>739</v>
       </c>
       <c r="J106" s="4">
         <v>105</v>
@@ -10408,9 +10556,8 @@
       <c r="K106" s="4">
         <v>105</v>
       </c>
-      <c r="L106" s="1"/>
       <c r="M106" s="4" t="s">
-        <v>719</v>
+        <v>739</v>
       </c>
       <c r="N106" s="4">
         <v>46.54</v>
@@ -10421,7 +10568,7 @@
     </row>
     <row r="107" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A107" s="4" t="s">
-        <v>721</v>
+        <v>741</v>
       </c>
       <c r="B107" s="4">
         <v>41.07</v>
@@ -10429,9 +10576,8 @@
       <c r="C107" s="4">
         <v>41.07</v>
       </c>
-      <c r="D107" s="1"/>
       <c r="E107" s="4" t="s">
-        <v>721</v>
+        <v>741</v>
       </c>
       <c r="F107" s="4">
         <v>72</v>
@@ -10439,9 +10585,8 @@
       <c r="G107" s="4">
         <v>72</v>
       </c>
-      <c r="H107" s="1"/>
       <c r="I107" s="4" t="s">
-        <v>721</v>
+        <v>741</v>
       </c>
       <c r="J107" s="4">
         <v>118</v>
@@ -10449,9 +10594,8 @@
       <c r="K107" s="4">
         <v>118</v>
       </c>
-      <c r="L107" s="1"/>
       <c r="M107" s="4" t="s">
-        <v>721</v>
+        <v>741</v>
       </c>
       <c r="N107" s="4">
         <v>50.2</v>
@@ -10462,7 +10606,7 @@
     </row>
     <row r="108" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A108" s="4" t="s">
-        <v>723</v>
+        <v>743</v>
       </c>
       <c r="B108" s="4">
         <v>50.2</v>
@@ -10470,9 +10614,8 @@
       <c r="C108" s="4">
         <v>50.2</v>
       </c>
-      <c r="D108" s="1"/>
       <c r="E108" s="4" t="s">
-        <v>723</v>
+        <v>743</v>
       </c>
       <c r="F108" s="4">
         <v>81.5</v>
@@ -10480,9 +10623,8 @@
       <c r="G108" s="4">
         <v>81.5</v>
       </c>
-      <c r="H108" s="1"/>
       <c r="I108" s="4" t="s">
-        <v>723</v>
+        <v>743</v>
       </c>
       <c r="J108" s="4">
         <v>145.6</v>
@@ -10490,9 +10632,8 @@
       <c r="K108" s="4">
         <v>145.6</v>
       </c>
-      <c r="L108" s="1"/>
       <c r="M108" s="4" t="s">
-        <v>723</v>
+        <v>743</v>
       </c>
       <c r="N108" s="4">
         <v>54.3</v>
@@ -10503,7 +10644,7 @@
     </row>
     <row r="109" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A109" s="4" t="s">
-        <v>725</v>
+        <v>745</v>
       </c>
       <c r="B109" s="4">
         <v>60</v>
@@ -10511,9 +10652,8 @@
       <c r="C109" s="4">
         <v>60</v>
       </c>
-      <c r="D109" s="1"/>
       <c r="E109" s="4" t="s">
-        <v>725</v>
+        <v>745</v>
       </c>
       <c r="F109" s="4">
         <v>90</v>
@@ -10521,9 +10661,8 @@
       <c r="G109" s="4">
         <v>90</v>
       </c>
-      <c r="H109" s="1"/>
       <c r="I109" s="4" t="s">
-        <v>725</v>
+        <v>745</v>
       </c>
       <c r="J109" s="4">
         <v>180</v>
@@ -10531,9 +10670,8 @@
       <c r="K109" s="4">
         <v>180</v>
       </c>
-      <c r="L109" s="1"/>
       <c r="M109" s="4" t="s">
-        <v>725</v>
+        <v>745</v>
       </c>
       <c r="N109" s="4">
         <v>57.3</v>
@@ -10544,7 +10682,7 @@
     </row>
     <row r="110" s="1" customFormat="1" customHeight="1" spans="13:15">
       <c r="M110" s="4" t="s">
-        <v>727</v>
+        <v>747</v>
       </c>
       <c r="N110" s="4">
         <v>60</v>
